--- a/Certifications/Snowpro Core/SnowProCore.xlsx
+++ b/Certifications/Snowpro Core/SnowProCore.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lahiru_10306\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dialogsl-my.sharepoint.com/personal/lahiru_nuwan_dialog_lk/Documents/Desktop/Certifications/Snowpro Core/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6F829D-7B29-4D13-B004-2A9C59841126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{1C6F829D-7B29-4D13-B004-2A9C59841126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E885627-6A37-4841-8982-CFA9317D2F3D}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1020" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="7" xr2:uid="{A1DD3791-2758-4015-950E-6866E350408A}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="325">
   <si>
     <t>Feature</t>
   </si>
@@ -1483,11 +1483,6 @@
     <t>With federated authentication enabled for your account, Snowflake still permits the maintenance and use of Snowflake user credentials, such as login names and passwords</t>
   </si>
   <si>
-    <t>When both an ALLOWED_IP_LIST and a BLOCKED_IP_LIST are used in a network policy,
- Snowflake applies the BLOCKED_IP_LIST first, denying access to any IPs on that list 
-regardless of whether they are also in the allowed list</t>
-  </si>
-  <si>
     <t>Table Types</t>
   </si>
   <si>
@@ -1810,9 +1805,6 @@
     <t>READER_ACCOUNT_USAGE</t>
   </si>
   <si>
-    <t>Network policies can be set at the User and Account levels in Snowflake</t>
-  </si>
-  <si>
     <t>Control inbound access to the Snowflake service and internal stage.</t>
   </si>
   <si>
@@ -1824,13 +1816,84 @@
   <si>
     <t>Network policies that existed before the introduction of network rules can no longer be 
 modified in Snowsight. Use the ALTER NETWORK POLICY command instead.</t>
+  </si>
+  <si>
+    <t>Access allowed from any computer or device by default.</t>
+  </si>
+  <si>
+    <t>Controlled By Security Administrator (or higher) role.</t>
+  </si>
+  <si>
+    <t>allowed lists and 
+blocked lists</t>
+  </si>
+  <si>
+    <t>If a network rule is added to the allowed list, all other identifiers of the same type 
+are implicitly denied—no need to use the blocked list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	If an identifier exists in both allowed and blocked lists, blocked list takes precedence.</t>
+  </si>
+  <si>
+    <t>If a private endpoint identifier is in the allowed list, any conflicting IP rules in the blocked list 
+are ignored—the private rule takes precedence.</t>
+  </si>
+  <si>
+    <t>Network rules with private identifiers (VPCE ID / LinkID) do not affect public network traffic.</t>
+  </si>
+  <si>
+    <t>Bypassing</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">You can temporarily bypass a network policy for a set number of minutes using the 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>`MINS_TO_BYPASS_NETWORK_POLICY`</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> property, but only Snowflake Support can set this value.</t>
+    </r>
+  </si>
+  <si>
+    <t>Network policy 
+precedence</t>
+  </si>
+  <si>
+    <t>You can apply a network policy to an account, a security integration, or a user</t>
+  </si>
+  <si>
+    <t>If there are network policies applied to more than one of these, the most specific network policy 
+overrides more general network policies</t>
+  </si>
+  <si>
+    <t>Account &gt; Security Integration &gt; User</t>
+  </si>
+  <si>
+    <t>NETWORK POLICIES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1943,8 +2006,16 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2047,6 +2118,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2069,7 +2152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2113,30 +2196,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2147,17 +2239,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2168,14 +2296,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2189,18 +2330,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2208,68 +2342,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2624,7 +2706,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -2632,21 +2714,21 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="25"/>
+      <c r="A3" s="40"/>
       <c r="B3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="25"/>
+      <c r="A4" s="40"/>
       <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="25"/>
+      <c r="A5" s="40"/>
       <c r="B5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2654,7 +2736,7 @@
       <c r="B6" s="5"/>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="40" t="s">
         <v>2</v>
       </c>
       <c r="B7" t="s">
@@ -2662,14 +2744,14 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="25"/>
+      <c r="A8" s="40"/>
       <c r="B8" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="25"/>
-      <c r="B9" s="24" t="s">
+      <c r="A9" s="40"/>
+      <c r="B9" s="23" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2678,7 +2760,7 @@
       <c r="B10" s="5"/>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="40" t="s">
         <v>3</v>
       </c>
       <c r="B11" t="s">
@@ -2686,13 +2768,13 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="25"/>
+      <c r="A12" s="40"/>
       <c r="B12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="25"/>
+      <c r="A13" s="40"/>
       <c r="B13" t="s">
         <v>11</v>
       </c>
@@ -2702,7 +2784,7 @@
       <c r="B14" s="5"/>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="40" t="s">
         <v>4</v>
       </c>
       <c r="B15" t="s">
@@ -2710,13 +2792,13 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="25"/>
+      <c r="A16" s="40"/>
       <c r="B16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="25"/>
+      <c r="A17" s="40"/>
       <c r="B17" t="s">
         <v>14</v>
       </c>
@@ -2754,98 +2836,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
     </row>
     <row r="2" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="41"/>
-      <c r="B5" s="28" t="s">
+      <c r="A5" s="62"/>
+      <c r="B5" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="41"/>
-      <c r="B6" s="28" t="s">
+      <c r="A6" s="62"/>
+      <c r="B6" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
     </row>
     <row r="7" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A7" s="41"/>
-      <c r="B7" s="38" t="s">
+      <c r="A7" s="62"/>
+      <c r="B7" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="41"/>
-      <c r="B8" s="28" t="s">
+      <c r="A8" s="62"/>
+      <c r="B8" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="13"/>
@@ -2858,45 +2940,45 @@
       <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="25"/>
-      <c r="B11" s="28" t="s">
+      <c r="A11" s="40"/>
+      <c r="B11" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="25"/>
-      <c r="B12" s="28" t="s">
+      <c r="A12" s="40"/>
+      <c r="B12" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="13"/>
@@ -2912,15 +2994,15 @@
       <c r="A14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="13"/>
@@ -2930,7 +3012,7 @@
       <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="40" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="14" t="s">
@@ -2938,98 +3020,98 @@
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="25"/>
-      <c r="B17" s="27" t="s">
+      <c r="A17" s="40"/>
+      <c r="B17" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
     </row>
     <row r="18" spans="1:9" ht="88.5" customHeight="1">
-      <c r="A18" s="25"/>
-      <c r="B18" s="37" t="s">
+      <c r="A18" s="40"/>
+      <c r="B18" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="25"/>
+      <c r="A19" s="40"/>
       <c r="B19" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="45" customHeight="1">
-      <c r="A20" s="25"/>
-      <c r="B20" s="37" t="s">
+      <c r="A20" s="40"/>
+      <c r="B20" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="25"/>
+      <c r="A21" s="40"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="25"/>
+      <c r="A22" s="40"/>
       <c r="B22" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="25"/>
-      <c r="B23" s="27" t="s">
+      <c r="A23" s="40"/>
+      <c r="B23" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
     </row>
     <row r="24" spans="1:9" ht="91.5" customHeight="1">
-      <c r="A24" s="25"/>
-      <c r="B24" s="38" t="s">
+      <c r="A24" s="40"/>
+      <c r="B24" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="25"/>
+      <c r="A25" s="40"/>
       <c r="B25" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="60" customHeight="1">
-      <c r="A26" s="25"/>
-      <c r="B26" s="38" t="s">
+      <c r="A26" s="40"/>
+      <c r="B26" s="63" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="13"/>
@@ -3043,16 +3125,16 @@
       <c r="I27" s="13"/>
     </row>
     <row r="28" spans="1:9" ht="39" customHeight="1">
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="63" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="13"/>
@@ -3066,97 +3148,82 @@
       <c r="I29" s="13"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="40" t="s">
         <v>81</v>
       </c>
       <c r="B30" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="25"/>
+      <c r="A31" s="40"/>
       <c r="B31" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="44"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="25"/>
+      <c r="A32" s="40"/>
       <c r="B32" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="25"/>
+      <c r="A33" s="40"/>
       <c r="B33" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
     </row>
     <row r="35" spans="1:10" ht="45.75" customHeight="1">
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="C33:I33"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B8:H8"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B18:H18"/>
@@ -3169,6 +3236,21 @@
     <mergeCell ref="C30:I30"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="C32:I32"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="C33:I33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3188,143 +3270,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="67" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
     </row>
     <row r="6" spans="1:13" ht="42.75" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="B10" s="52" t="s">
+      <c r="B10" s="68" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="13"/>
@@ -3342,41 +3424,41 @@
       <c r="M11" s="13"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="44" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="25"/>
-      <c r="B13" s="28" t="s">
+      <c r="A13" s="40"/>
+      <c r="B13" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="25"/>
+      <c r="A14" s="40"/>
       <c r="B14" s="16" t="s">
         <v>110</v>
       </c>
@@ -3392,23 +3474,23 @@
       <c r="L14" s="6"/>
     </row>
     <row r="15" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A15" s="25"/>
-      <c r="C15" s="44" t="s">
+      <c r="A15" s="40"/>
+      <c r="C15" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="25"/>
+      <c r="A16" s="40"/>
       <c r="B16" s="17" t="s">
         <v>109</v>
       </c>
@@ -3416,67 +3498,67 @@
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="25"/>
-      <c r="C17" s="53" t="s">
+      <c r="A17" s="40"/>
+      <c r="C17" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="53"/>
+      <c r="D17" s="69"/>
     </row>
     <row r="18" spans="1:15" ht="45.75" customHeight="1">
-      <c r="A18" s="25"/>
-      <c r="D18" s="44" t="s">
+      <c r="A18" s="40"/>
+      <c r="D18" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="44"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="44"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="57"/>
+      <c r="N18" s="57"/>
     </row>
     <row r="19" spans="1:15" ht="20.25" customHeight="1">
-      <c r="A19" s="25"/>
-      <c r="D19" s="44" t="s">
+      <c r="A19" s="40"/>
+      <c r="D19" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="44"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="25"/>
-      <c r="C20" s="53" t="s">
+      <c r="A20" s="40"/>
+      <c r="C20" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="53"/>
+      <c r="D20" s="69"/>
     </row>
     <row r="21" spans="1:15" ht="27" customHeight="1">
-      <c r="A21" s="25"/>
-      <c r="D21" s="36" t="s">
+      <c r="A21" s="40"/>
+      <c r="D21" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
+      <c r="K21" s="56"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="56"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="13"/>
@@ -3496,192 +3578,192 @@
       <c r="O22" s="13"/>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="49" t="s">
+      <c r="B23" s="70" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="45"/>
-      <c r="C24" s="28" t="s">
+      <c r="A24" s="71"/>
+      <c r="C24" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="28"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="44"/>
+      <c r="O24" s="44"/>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="45"/>
-      <c r="C25" s="28" t="s">
+      <c r="A25" s="71"/>
+      <c r="C25" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="44"/>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="45"/>
-      <c r="C26" s="28" t="s">
+      <c r="A26" s="71"/>
+      <c r="C26" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="44"/>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="45"/>
-      <c r="B27" s="49" t="s">
+      <c r="A27" s="71"/>
+      <c r="B27" s="70" t="s">
         <v>121</v>
       </c>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="45"/>
-      <c r="C28" s="28" t="s">
+      <c r="A28" s="71"/>
+      <c r="C28" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="45"/>
-      <c r="C29" s="28" t="s">
+      <c r="A29" s="71"/>
+      <c r="C29" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="45"/>
-      <c r="C30" s="28" t="s">
+      <c r="A30" s="71"/>
+      <c r="C30" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="45"/>
-      <c r="B31" s="49" t="s">
+      <c r="A31" s="71"/>
+      <c r="B31" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="45"/>
-      <c r="C32" s="46" t="s">
+      <c r="A32" s="71"/>
+      <c r="C32" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="46"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="45"/>
-      <c r="C33" s="46" t="s">
+      <c r="A33" s="71"/>
+      <c r="C33" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="46"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="45"/>
-      <c r="C34" s="28" t="s">
+      <c r="A34" s="71"/>
+      <c r="C34" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="45"/>
+      <c r="A35" s="71"/>
       <c r="B35" s="18" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="45"/>
-      <c r="C36" s="28" t="s">
+      <c r="A36" s="71"/>
+      <c r="C36" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="45"/>
-      <c r="C37" s="28" t="s">
+      <c r="A37" s="71"/>
+      <c r="C37" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="45"/>
-      <c r="C38" s="28" t="s">
+      <c r="A38" s="71"/>
+      <c r="C38" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="45"/>
+      <c r="A39" s="71"/>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="13"/>
@@ -3701,132 +3783,160 @@
       <c r="O40" s="13"/>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="B41" s="47" t="s">
+      <c r="B41" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="C41" s="47"/>
+      <c r="C41" s="73"/>
     </row>
     <row r="42" spans="1:16" ht="40.5" customHeight="1">
-      <c r="A42" s="25"/>
-      <c r="C42" s="48" t="s">
+      <c r="A42" s="40"/>
+      <c r="C42" s="74" t="s">
         <v>134</v>
       </c>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
-      <c r="L42" s="48"/>
-      <c r="M42" s="48"/>
-      <c r="N42" s="48"/>
-      <c r="O42" s="48"/>
-      <c r="P42" s="48"/>
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="74"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="74"/>
+      <c r="L42" s="74"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="74"/>
+      <c r="P42" s="74"/>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" s="25"/>
-      <c r="B43" s="47" t="s">
+      <c r="A43" s="40"/>
+      <c r="B43" s="73" t="s">
         <v>135</v>
       </c>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
+      <c r="C43" s="73"/>
+      <c r="D43" s="73"/>
     </row>
     <row r="44" spans="1:16" ht="54" customHeight="1">
-      <c r="A44" s="25"/>
-      <c r="C44" s="48" t="s">
+      <c r="A44" s="40"/>
+      <c r="C44" s="74" t="s">
         <v>136</v>
       </c>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
-      <c r="L44" s="48"/>
-      <c r="M44" s="48"/>
-      <c r="N44" s="48"/>
-      <c r="O44" s="48"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="74"/>
+      <c r="H44" s="74"/>
+      <c r="I44" s="74"/>
+      <c r="J44" s="74"/>
+      <c r="K44" s="74"/>
+      <c r="L44" s="74"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="74"/>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" s="25"/>
-      <c r="B45" s="47" t="s">
+      <c r="A45" s="40"/>
+      <c r="B45" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="C45" s="47"/>
+      <c r="C45" s="73"/>
     </row>
     <row r="46" spans="1:16">
-      <c r="A46" s="25"/>
-      <c r="C46" s="28" t="s">
+      <c r="A46" s="40"/>
+      <c r="C46" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="44"/>
     </row>
     <row r="47" spans="1:16">
-      <c r="A47" s="25"/>
-      <c r="C47" s="28" t="s">
+      <c r="A47" s="40"/>
+      <c r="C47" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-    </row>
-    <row r="48" spans="1:16" s="79" customFormat="1"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+    </row>
+    <row r="48" spans="1:16" s="38" customFormat="1"/>
     <row r="49" spans="1:12" ht="46.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B49" s="44" t="s">
         <v>275</v>
       </c>
-      <c r="C49" s="36"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="36"/>
-      <c r="K49" s="36"/>
-      <c r="L49" s="36"/>
+      <c r="B49" s="57" t="s">
+        <v>274</v>
+      </c>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="56"/>
+      <c r="L49" s="56"/>
     </row>
     <row r="51" spans="1:12" ht="55.5" customHeight="1">
       <c r="A51" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B51" s="65" t="s">
         <v>298</v>
       </c>
-      <c r="B51" s="81" t="s">
-        <v>299</v>
-      </c>
-      <c r="C51" s="81"/>
-      <c r="D51" s="81"/>
-      <c r="E51" s="81"/>
-      <c r="F51" s="81"/>
-      <c r="G51" s="81"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="81"/>
-      <c r="J51" s="81"/>
-      <c r="K51" s="81"/>
+      <c r="C51" s="65"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="65"/>
+      <c r="H51" s="65"/>
+      <c r="I51" s="65"/>
+      <c r="J51" s="65"/>
+      <c r="K51" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="A23:A39"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C47:K47"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="C42:P42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="C44:O44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="C46:K46"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="D18:N18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="D19:O19"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="D21:N21"/>
+    <mergeCell ref="C24:O24"/>
+    <mergeCell ref="C25:O25"/>
+    <mergeCell ref="C26:O26"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B49:L49"/>
     <mergeCell ref="B51:K51"/>
     <mergeCell ref="B13:L13"/>
@@ -3843,34 +3953,6 @@
     <mergeCell ref="A12:A21"/>
     <mergeCell ref="C15:L15"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="D18:N18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="D19:O19"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="C38:I38"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="D21:N21"/>
-    <mergeCell ref="C24:O24"/>
-    <mergeCell ref="C25:O25"/>
-    <mergeCell ref="C26:O26"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="A23:A39"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="C47:K47"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="C42:P42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="C44:O44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="C46:K46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3887,198 +3969,193 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="76" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1">
+      <c r="A2" s="75" t="s">
+        <v>284</v>
+      </c>
+      <c r="B2" s="75"/>
+      <c r="C2" s="44" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-    </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1">
-      <c r="A2" s="83" t="s">
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+    </row>
+    <row r="3" spans="1:12" ht="34.5" customHeight="1">
+      <c r="A3" s="75"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="57" t="s">
+        <v>278</v>
+      </c>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="75"/>
+      <c r="B4" s="75"/>
+    </row>
+    <row r="5" spans="1:12" ht="38.25" customHeight="1">
+      <c r="A5" s="75"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D5" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+    </row>
+    <row r="6" spans="1:12" s="22" customFormat="1" ht="83.25" customHeight="1">
+      <c r="A6" s="75"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>282</v>
+      </c>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+    </row>
+    <row r="7" spans="1:12" s="22" customFormat="1" ht="18" customHeight="1">
+      <c r="A7" s="75"/>
+      <c r="B7" s="75"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="57" t="s">
+        <v>289</v>
+      </c>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="39"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="B9" s="40"/>
+      <c r="C9" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
+    </row>
+    <row r="10" spans="1:12" ht="41.25" customHeight="1">
+      <c r="A10" s="40"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="57" t="s">
         <v>285</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-    </row>
-    <row r="3" spans="1:12" ht="34.5" customHeight="1">
-      <c r="A3" s="83"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="44" t="s">
-        <v>279</v>
-      </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="83"/>
-      <c r="B4" s="83"/>
-    </row>
-    <row r="5" spans="1:12" ht="38.25" customHeight="1">
-      <c r="A5" s="83"/>
-      <c r="B5" s="83"/>
-      <c r="C5" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>281</v>
-      </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-    </row>
-    <row r="6" spans="1:12" s="22" customFormat="1" ht="83.25" customHeight="1">
-      <c r="A6" s="83"/>
-      <c r="B6" s="83"/>
-      <c r="C6" s="25" t="s">
-        <v>282</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>283</v>
-      </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-    </row>
-    <row r="7" spans="1:12" s="22" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="83"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="44" t="s">
-        <v>290</v>
-      </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="82"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="82"/>
-      <c r="L8" s="82"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="25" t="s">
-        <v>284</v>
-      </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="28" t="s">
-        <v>289</v>
-      </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-    </row>
-    <row r="10" spans="1:12" ht="41.25" customHeight="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="44" t="s">
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+    </row>
+    <row r="11" spans="1:12" ht="19.5" customHeight="1">
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="56" t="s">
         <v>286</v>
       </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-    </row>
-    <row r="11" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="36" t="s">
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="56"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="40"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="44" t="s">
         <v>287</v>
       </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="28" t="s">
-        <v>288</v>
-      </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C10:L10"/>
-    <mergeCell ref="C9:L9"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="C12:L12"/>
-    <mergeCell ref="A9:B12"/>
     <mergeCell ref="D7:L7"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="A2:B7"/>
@@ -4087,6 +4164,11 @@
     <mergeCell ref="C3:L3"/>
     <mergeCell ref="D5:L5"/>
     <mergeCell ref="D6:L6"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="C12:L12"/>
+    <mergeCell ref="A9:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4105,95 +4187,95 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
     </row>
     <row r="3" spans="1:9" ht="20.25" customHeight="1">
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="48" t="s">
         <v>177</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
     </row>
     <row r="5" spans="1:9" ht="21" customHeight="1">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="56" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="77" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="49" t="s">
         <v>184</v>
       </c>
-      <c r="B11" s="27"/>
+      <c r="B11" s="49"/>
     </row>
     <row r="12" spans="1:9">
       <c r="B12" t="s">
@@ -4209,15 +4291,15 @@
       <c r="A15" t="s">
         <v>255</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="63" t="s">
         <v>256</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4304,18 +4386,18 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B8" t="s">
         <v>292</v>
-      </c>
-      <c r="B8" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B9" t="s">
         <v>306</v>
-      </c>
-      <c r="B9" t="s">
-        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -4344,74 +4426,74 @@
       <c r="A3" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="57" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="B5" s="25"/>
-      <c r="C5" s="28" t="s">
+      <c r="B5" s="40"/>
+      <c r="C5" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="B6" s="25"/>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="40"/>
+      <c r="C6" s="44" t="s">
         <v>151</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="B7" s="25"/>
-      <c r="C7" s="28" t="s">
+      <c r="B7" s="40"/>
+      <c r="C7" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="B8" s="25"/>
-      <c r="C8" s="28" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4445,112 +4527,112 @@
         <v>43</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="78" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4579,61 +4661,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
     </row>
     <row r="6" spans="1:13">
       <c r="B6" s="6"/>
@@ -4647,173 +4729,173 @@
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
     </row>
     <row r="17" spans="1:9" ht="39.75" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27" t="s">
+      <c r="A20" s="48"/>
+      <c r="B20" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27" t="s">
+      <c r="A23" s="48"/>
+      <c r="B23" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
     </row>
     <row r="27" spans="1:9" ht="30">
       <c r="A27" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
     </row>
     <row r="29" spans="1:9">
       <c r="B29" t="s">
@@ -4822,17 +4904,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="B12:M12"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B10:H10"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="B23:I23"/>
@@ -4841,6 +4912,17 @@
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B12:M12"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B9:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -5004,12 +5086,12 @@
     </row>
     <row r="51" spans="1:2" ht="90">
       <c r="B51" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="45">
       <c r="B53" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -5033,188 +5115,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.5">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="61" t="s">
+      <c r="B2" s="51"/>
+      <c r="C2" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="60"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="62" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="60"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="61" t="s">
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="60"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
     </row>
     <row r="6" spans="1:5" ht="30">
-      <c r="A6" s="60"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="62" t="s">
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="60"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="60"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="30">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="62" t="s">
+      <c r="A9" s="51"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-    </row>
-    <row r="10" spans="1:5" s="56" customFormat="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-    </row>
-    <row r="11" spans="1:5" s="56" customFormat="1">
-      <c r="A11" s="59" t="s">
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="50" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="67"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="52"/>
+      <c r="C11" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="67"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="61" t="s">
+      <c r="A12" s="52"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="67"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="61" t="s">
+      <c r="A13" s="52"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-    </row>
-    <row r="14" spans="1:5" s="56" customFormat="1">
-      <c r="A14" s="66"/>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="69" t="s">
+      <c r="A15" s="50" t="s">
         <v>238</v>
       </c>
-      <c r="B15" s="70"/>
-      <c r="C15" s="71" t="s">
+      <c r="B15" s="52"/>
+      <c r="C15" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D15" s="71" t="s">
+      <c r="D15" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="71" t="s">
+      <c r="E15" s="32" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="45">
-      <c r="A16" s="70"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="61" t="s">
+      <c r="A16" s="52"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="D16" s="62" t="s">
+      <c r="D16" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="E16" s="62" t="s">
+      <c r="E16" s="27" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="70"/>
-      <c r="B17" s="70"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61" t="s">
+      <c r="A17" s="52"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="E17" s="61"/>
+      <c r="E17" s="26"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="70"/>
-      <c r="B18" s="70"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61" t="s">
+      <c r="A18" s="52"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="E18" s="61"/>
+      <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="70"/>
-      <c r="B19" s="70"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
+      <c r="A19" s="52"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
     </row>
     <row r="20" spans="1:5" ht="30">
-      <c r="A20" s="70"/>
-      <c r="B20" s="70"/>
-      <c r="C20" s="61" t="s">
+      <c r="A20" s="52"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D20" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="E20" s="62" t="s">
+      <c r="E20" s="27" t="s">
         <v>246</v>
       </c>
     </row>
@@ -5294,35 +5376,35 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B3" t="s">
         <v>223</v>
       </c>
       <c r="C3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30">
       <c r="A4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B4" t="s">
         <v>223</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30">
       <c r="A5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B5" t="s">
         <v>223</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -5340,13 +5422,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30.75" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="55" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
@@ -5355,52 +5437,52 @@
       <c r="B2" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
     </row>
     <row r="3" spans="1:13">
       <c r="B3" t="s">
         <v>157</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
     </row>
     <row r="4" spans="1:13">
       <c r="B4" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -5409,53 +5491,53 @@
       <c r="B6" t="s">
         <v>162</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
     </row>
     <row r="7" spans="1:13">
       <c r="B7" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="44" t="s">
         <v>165</v>
       </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
     </row>
     <row r="8" spans="1:13">
       <c r="B8" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5476,91 +5558,319 @@
   <sheetPr>
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.25" customHeight="1">
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
+    <row r="1" spans="1:16" s="79" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A1" s="81" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" t="s">
+      <c r="A2" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="56" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="40"/>
+      <c r="B3" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="40"/>
+      <c r="B4" s="56" t="s">
+        <v>311</v>
+      </c>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="40"/>
+      <c r="B5" s="56" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="82"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+    </row>
+    <row r="7" spans="1:16" ht="43.5" customHeight="1">
+      <c r="A7" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="B3" s="28" t="s">
+      <c r="B7" s="57" t="s">
         <v>310</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-    </row>
-    <row r="6" spans="1:16" ht="43.5" customHeight="1">
-      <c r="A6" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>312</v>
-      </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-    </row>
-    <row r="20" spans="10:20">
-      <c r="J20" s="44" t="s">
-        <v>257</v>
-      </c>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="44"/>
-      <c r="S20" s="44"/>
-      <c r="T20" s="44"/>
-    </row>
-    <row r="22" spans="10:20">
-      <c r="J22" t="s">
-        <v>308</v>
-      </c>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="82"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="82"/>
+    </row>
+    <row r="9" spans="1:16" ht="38.25" customHeight="1">
+      <c r="A9" s="71" t="s">
+        <v>313</v>
+      </c>
+      <c r="B9" s="57" t="s">
+        <v>314</v>
+      </c>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+    </row>
+    <row r="10" spans="1:16" ht="20.25" customHeight="1">
+      <c r="A10" s="71"/>
+      <c r="B10" s="56" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+    </row>
+    <row r="11" spans="1:16" ht="41.25" customHeight="1">
+      <c r="A11" s="71"/>
+      <c r="B11" s="57" t="s">
+        <v>316</v>
+      </c>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+    </row>
+    <row r="12" spans="1:16" ht="21" customHeight="1">
+      <c r="A12" s="71"/>
+      <c r="B12" s="56" t="s">
+        <v>317</v>
+      </c>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="56"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="82"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+    </row>
+    <row r="14" spans="1:16" ht="43.5" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B14" s="57" t="s">
+        <v>319</v>
+      </c>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="82"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="82"/>
+    </row>
+    <row r="16" spans="1:16" ht="30" customHeight="1">
+      <c r="A16" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="B16" s="56" t="s">
+        <v>321</v>
+      </c>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+    </row>
+    <row r="17" spans="1:20" ht="30" customHeight="1">
+      <c r="A17" s="71"/>
+      <c r="B17" s="57" t="s">
+        <v>322</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" s="71"/>
+      <c r="B18" s="48" t="s">
+        <v>323</v>
+      </c>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="57"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="J20:T20"/>
+  <mergeCells count="18">
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="B11:K11"/>
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="J21:T21"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B14:L14"/>
+    <mergeCell ref="B16:K16"/>
+    <mergeCell ref="B17:K17"/>
+    <mergeCell ref="B18:K18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5583,105 +5893,105 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="C2" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="D2" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="D2" s="78" t="s">
+      <c r="E2" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="F2" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="F2" s="78" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="45">
+      <c r="A3" s="40"/>
+      <c r="B3" s="37" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="45">
-      <c r="A3" s="25"/>
-      <c r="B3" s="78" t="s">
+      <c r="C3" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="D3" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="E3" s="24" t="s">
         <v>266</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="F3" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="F3" s="58" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="30">
+      <c r="A4" s="40"/>
+      <c r="B4" s="37" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="30">
-      <c r="A4" s="25"/>
-      <c r="B4" s="78" t="s">
+      <c r="C4" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="D4" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="D4" s="76" t="s">
+      <c r="E4" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="E4" s="75" t="s">
+      <c r="F4" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30">
+      <c r="A5" s="40"/>
+      <c r="B5" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="F4" s="58" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="30">
-      <c r="A5" s="25"/>
-      <c r="B5" s="78" t="s">
+      <c r="C5" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="40"/>
+      <c r="B6" s="37" t="s">
         <v>273</v>
       </c>
-      <c r="C5" s="74" t="s">
+      <c r="C6" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="D5" s="76" t="s">
-        <v>271</v>
-      </c>
-      <c r="E5" s="75" t="s">
-        <v>272</v>
-      </c>
-      <c r="F5" s="58" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="25"/>
-      <c r="B6" s="78" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="76" t="s">
-        <v>271</v>
-      </c>
-      <c r="D6" s="76" t="s">
-        <v>271</v>
-      </c>
-      <c r="E6" s="77" t="s">
-        <v>271</v>
-      </c>
-      <c r="F6" s="58" t="s">
-        <v>268</v>
+      <c r="D6" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="41.25" customHeight="1">
-      <c r="B8" s="44" t="s">
-        <v>291</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
+      <c r="B8" s="57" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Certifications/Snowpro Core/SnowProCore.xlsx
+++ b/Certifications/Snowpro Core/SnowProCore.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dialogsl-my.sharepoint.com/personal/lahiru_nuwan_dialog_lk/Documents/Desktop/Certifications/Snowpro Core/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{1C6F829D-7B29-4D13-B004-2A9C59841126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E885627-6A37-4841-8982-CFA9317D2F3D}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{1C6F829D-7B29-4D13-B004-2A9C59841126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACA6BE47-0C2D-4EF4-A204-5A24DE393676}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1020" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="7" xr2:uid="{A1DD3791-2758-4015-950E-6866E350408A}"/>
+    <workbookView xWindow="-28920" yWindow="-1020" windowWidth="29040" windowHeight="15840" xr2:uid="{A1DD3791-2758-4015-950E-6866E350408A}"/>
   </bookViews>
   <sheets>
     <sheet name="SF Editions" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="328">
   <si>
     <t>Feature</t>
   </si>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>Automatic Scaling</t>
-  </si>
-  <si>
-    <t>Materialized Views</t>
   </si>
   <si>
     <t>Failover &amp; Replication</t>
@@ -1887,6 +1884,18 @@
   </si>
   <si>
     <t>NETWORK POLICIES</t>
+  </si>
+  <si>
+    <t>Which encryption type will enable client-side encryption for a directory table?</t>
+  </si>
+  <si>
+    <t>SNOWFLAKE_FULL</t>
+  </si>
+  <si>
+    <t>Query acceleration | Search optimization | Iceberg tables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failover and failback and Redirecting client connections </t>
   </si>
 </sst>
 </file>
@@ -2152,7 +2161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2227,8 +2236,30 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2238,24 +2269,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2278,14 +2291,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2296,11 +2318,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2311,24 +2348,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2342,16 +2361,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2689,7 +2699,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2699,14 +2709,14 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -2714,21 +2724,18 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="40"/>
+      <c r="A3" s="42"/>
       <c r="B3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="40"/>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A4" s="42"/>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="40"/>
+      <c r="A5" s="42"/>
       <c r="B5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2736,84 +2743,96 @@
       <c r="B6" s="5"/>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="83" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="42"/>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="42"/>
+      <c r="B9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="42"/>
+      <c r="B10" s="23" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="40"/>
-      <c r="B8" t="s">
+    <row r="11" spans="1:2">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="42"/>
+      <c r="B13" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="42"/>
+      <c r="B14" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="42"/>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="42"/>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="42"/>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="B20" t="s">
         <v>217</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="40"/>
-      <c r="B9" s="23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="40"/>
-      <c r="B12" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="40"/>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="40"/>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="40"/>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="B18" t="s">
-        <v>218</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A7:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2836,98 +2855,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+    </row>
+    <row r="2" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A2" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-    </row>
-    <row r="2" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A2" s="61" t="s">
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="40" t="s">
+      <c r="B4" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="67"/>
+      <c r="B5" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="62"/>
-      <c r="B5" s="44" t="s">
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="67"/>
+      <c r="B6" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="62"/>
-      <c r="B6" s="44" t="s">
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+    </row>
+    <row r="7" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A7" s="67"/>
+      <c r="B7" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-    </row>
-    <row r="7" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A7" s="62"/>
-      <c r="B7" s="63" t="s">
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="67"/>
+      <c r="B8" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="62"/>
-      <c r="B8" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="13"/>
@@ -2940,45 +2959,45 @@
       <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="44" t="s">
+      <c r="A10" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="42"/>
+      <c r="B11" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="40"/>
-      <c r="B11" s="44" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="42"/>
+      <c r="B12" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="40"/>
-      <c r="B12" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="13"/>
@@ -2992,17 +3011,17 @@
     </row>
     <row r="14" spans="1:13" ht="45" customHeight="1">
       <c r="A14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="57" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="13"/>
@@ -3012,106 +3031,106 @@
       <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="42"/>
+      <c r="B17" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+    </row>
+    <row r="18" spans="1:9" ht="88.5" customHeight="1">
+      <c r="A18" s="42"/>
+      <c r="B18" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="42"/>
+      <c r="B19" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="40"/>
-      <c r="B17" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-    </row>
-    <row r="18" spans="1:9" ht="88.5" customHeight="1">
-      <c r="A18" s="40"/>
-      <c r="B18" s="64" t="s">
+    <row r="20" spans="1:9" ht="45" customHeight="1">
+      <c r="A20" s="42"/>
+      <c r="B20" s="63" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="42"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="42"/>
+      <c r="B22" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="42"/>
+      <c r="B23" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+    </row>
+    <row r="24" spans="1:9" ht="91.5" customHeight="1">
+      <c r="A24" s="42"/>
+      <c r="B24" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="42"/>
+      <c r="B25" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="60" customHeight="1">
+      <c r="A26" s="42"/>
+      <c r="B26" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="64"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="40"/>
-      <c r="B19" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="45" customHeight="1">
-      <c r="A20" s="40"/>
-      <c r="B20" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="40"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="40"/>
-      <c r="B22" s="14" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="40"/>
-      <c r="B23" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-    </row>
-    <row r="24" spans="1:9" ht="91.5" customHeight="1">
-      <c r="A24" s="40"/>
-      <c r="B24" s="63" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="40"/>
-      <c r="B25" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="60" customHeight="1">
-      <c r="A26" s="40"/>
-      <c r="B26" s="63" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="13"/>
@@ -3125,16 +3144,16 @@
       <c r="I27" s="13"/>
     </row>
     <row r="28" spans="1:9" ht="39" customHeight="1">
-      <c r="B28" s="63" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
+      <c r="B28" s="64" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="64"/>
+      <c r="I28" s="64"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="13"/>
@@ -3148,82 +3167,97 @@
       <c r="I29" s="13"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="40" t="s">
+      <c r="A30" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" t="s">
         <v>81</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="44" t="s">
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="42"/>
+      <c r="B31" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="40"/>
-      <c r="B31" t="s">
+      <c r="C31" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="44" t="s">
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="42"/>
+      <c r="B32" t="s">
         <v>85</v>
       </c>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="44"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="40"/>
-      <c r="B32" t="s">
+      <c r="C32" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="44" t="s">
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="42"/>
+      <c r="B33" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="40"/>
-      <c r="B33" t="s">
+      <c r="C33" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
     </row>
     <row r="35" spans="1:10" ht="45.75" customHeight="1">
-      <c r="B35" s="58" t="s">
-        <v>193</v>
-      </c>
-      <c r="C35" s="59"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="59"/>
-      <c r="J35" s="59"/>
+      <c r="B35" s="68" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B8:H8"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B18:H18"/>
@@ -3236,21 +3270,6 @@
     <mergeCell ref="C30:I30"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="C32:I32"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="C33:I33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3270,143 +3289,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
+      <c r="A1" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
+        <v>45</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="67" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
     </row>
     <row r="6" spans="1:13" ht="42.75" customHeight="1">
       <c r="A6" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
+        <v>99</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="78" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="C9" s="78"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="78"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="B10" s="78" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="B10" s="68" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="68"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="78"/>
+      <c r="I10" s="78"/>
+      <c r="J10" s="78"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="13"/>
@@ -3424,43 +3443,43 @@
       <c r="M11" s="13"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="40"/>
-      <c r="B13" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="40"/>
+      <c r="A14" s="42"/>
       <c r="B14" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -3474,91 +3493,91 @@
       <c r="L14" s="6"/>
     </row>
     <row r="15" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A15" s="40"/>
-      <c r="C15" s="57" t="s">
+      <c r="A15" s="42"/>
+      <c r="C15" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="8"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="42"/>
+      <c r="B16" s="17" t="s">
         <v>108</v>
-      </c>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="57"/>
-      <c r="M15" s="8"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="40"/>
-      <c r="B16" s="17" t="s">
-        <v>109</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="40"/>
-      <c r="C17" s="69" t="s">
+      <c r="A17" s="42"/>
+      <c r="C17" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="74"/>
+    </row>
+    <row r="18" spans="1:15" ht="45.75" customHeight="1">
+      <c r="A18" s="42"/>
+      <c r="D18" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="69"/>
-    </row>
-    <row r="18" spans="1:15" ht="45.75" customHeight="1">
-      <c r="A18" s="40"/>
-      <c r="D18" s="57" t="s">
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="62"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="62"/>
+    </row>
+    <row r="19" spans="1:15" ht="20.25" customHeight="1">
+      <c r="A19" s="42"/>
+      <c r="D19" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="62"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="62"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="42"/>
+      <c r="C20" s="74" t="s">
         <v>112</v>
       </c>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="57"/>
-      <c r="N18" s="57"/>
-    </row>
-    <row r="19" spans="1:15" ht="20.25" customHeight="1">
-      <c r="A19" s="40"/>
-      <c r="D19" s="57" t="s">
+      <c r="D20" s="74"/>
+    </row>
+    <row r="21" spans="1:15" ht="27" customHeight="1">
+      <c r="A21" s="42"/>
+      <c r="D21" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="57"/>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="40"/>
-      <c r="C20" s="69" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="69"/>
-    </row>
-    <row r="21" spans="1:15" ht="27" customHeight="1">
-      <c r="A21" s="40"/>
-      <c r="D21" s="56" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="56"/>
-      <c r="K21" s="56"/>
-      <c r="L21" s="56"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="56"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="58"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="58"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="13"/>
@@ -3578,192 +3597,192 @@
       <c r="O22" s="13"/>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="71" t="s">
+      <c r="A23" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="73" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="70" t="s">
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="59"/>
+      <c r="C24" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="70"/>
-      <c r="D23" s="70"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="71"/>
-      <c r="C24" s="44" t="s">
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="45"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="59"/>
+      <c r="C25" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44"/>
-      <c r="K24" s="44"/>
-      <c r="L24" s="44"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="44"/>
-      <c r="O24" s="44"/>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="71"/>
-      <c r="C25" s="44" t="s">
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="59"/>
+      <c r="C26" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="44"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="44"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="44"/>
-      <c r="O25" s="44"/>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="71"/>
-      <c r="C26" s="44" t="s">
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="59"/>
+      <c r="B27" s="73" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="44"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="71"/>
-      <c r="B27" s="70" t="s">
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="59"/>
+      <c r="C28" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="71"/>
-      <c r="C28" s="44" t="s">
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="59"/>
+      <c r="C29" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" s="71"/>
-      <c r="C29" s="44" t="s">
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="59"/>
+      <c r="C30" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="71"/>
-      <c r="C30" s="44" t="s">
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="59"/>
+      <c r="B31" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="A31" s="71"/>
-      <c r="B31" s="70" t="s">
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="59"/>
+      <c r="C32" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="71"/>
-      <c r="C32" s="72" t="s">
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="59"/>
+      <c r="C33" s="70" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-    </row>
-    <row r="33" spans="1:16">
-      <c r="A33" s="71"/>
-      <c r="C33" s="72" t="s">
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="59"/>
+      <c r="C34" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="72"/>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="A34" s="71"/>
-      <c r="C34" s="44" t="s">
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="45"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="59"/>
+      <c r="B35" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="44"/>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="A35" s="71"/>
-      <c r="B35" s="18" t="s">
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="59"/>
+      <c r="C36" s="45" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="71"/>
-      <c r="C36" s="44" t="s">
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="59"/>
+      <c r="C37" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="44"/>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="71"/>
-      <c r="C37" s="44" t="s">
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="59"/>
+      <c r="C38" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="D37" s="44"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="44"/>
-    </row>
-    <row r="38" spans="1:16">
-      <c r="A38" s="71"/>
-      <c r="C38" s="44" t="s">
-        <v>132</v>
-      </c>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="44"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="71"/>
+      <c r="A39" s="59"/>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="13"/>
@@ -3783,132 +3802,160 @@
       <c r="O40" s="13"/>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="B41" s="73" t="s">
+      <c r="A41" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="B41" s="71" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" s="71"/>
+    </row>
+    <row r="42" spans="1:16" ht="40.5" customHeight="1">
+      <c r="A42" s="42"/>
+      <c r="C42" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="C41" s="73"/>
-    </row>
-    <row r="42" spans="1:16" ht="40.5" customHeight="1">
-      <c r="A42" s="40"/>
-      <c r="C42" s="74" t="s">
+      <c r="D42" s="72"/>
+      <c r="E42" s="72"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="72"/>
+      <c r="H42" s="72"/>
+      <c r="I42" s="72"/>
+      <c r="J42" s="72"/>
+      <c r="K42" s="72"/>
+      <c r="L42" s="72"/>
+      <c r="M42" s="72"/>
+      <c r="N42" s="72"/>
+      <c r="O42" s="72"/>
+      <c r="P42" s="72"/>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="42"/>
+      <c r="B43" s="71" t="s">
         <v>134</v>
       </c>
-      <c r="D42" s="74"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="74"/>
-      <c r="I42" s="74"/>
-      <c r="J42" s="74"/>
-      <c r="K42" s="74"/>
-      <c r="L42" s="74"/>
-      <c r="M42" s="74"/>
-      <c r="N42" s="74"/>
-      <c r="O42" s="74"/>
-      <c r="P42" s="74"/>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43" s="40"/>
-      <c r="B43" s="73" t="s">
+      <c r="C43" s="71"/>
+      <c r="D43" s="71"/>
+    </row>
+    <row r="44" spans="1:16" ht="54" customHeight="1">
+      <c r="A44" s="42"/>
+      <c r="C44" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="C43" s="73"/>
-      <c r="D43" s="73"/>
-    </row>
-    <row r="44" spans="1:16" ht="54" customHeight="1">
-      <c r="A44" s="40"/>
-      <c r="C44" s="74" t="s">
+      <c r="D44" s="72"/>
+      <c r="E44" s="72"/>
+      <c r="F44" s="72"/>
+      <c r="G44" s="72"/>
+      <c r="H44" s="72"/>
+      <c r="I44" s="72"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="72"/>
+      <c r="L44" s="72"/>
+      <c r="M44" s="72"/>
+      <c r="N44" s="72"/>
+      <c r="O44" s="72"/>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="42"/>
+      <c r="B45" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="D44" s="74"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="74"/>
-      <c r="H44" s="74"/>
-      <c r="I44" s="74"/>
-      <c r="J44" s="74"/>
-      <c r="K44" s="74"/>
-      <c r="L44" s="74"/>
-      <c r="M44" s="74"/>
-      <c r="N44" s="74"/>
-      <c r="O44" s="74"/>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="A45" s="40"/>
-      <c r="B45" s="73" t="s">
+      <c r="C45" s="71"/>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="42"/>
+      <c r="C46" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="C45" s="73"/>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46" s="40"/>
-      <c r="C46" s="44" t="s">
+      <c r="D46" s="45"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="45"/>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="42"/>
+      <c r="C47" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="44"/>
-      <c r="K46" s="44"/>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="A47" s="40"/>
-      <c r="C47" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="D47" s="44"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="44"/>
-      <c r="I47" s="44"/>
-      <c r="J47" s="44"/>
-      <c r="K47" s="44"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="45"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
     </row>
     <row r="48" spans="1:16" s="38" customFormat="1"/>
     <row r="49" spans="1:12" ht="46.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B49" s="57" t="s">
         <v>274</v>
       </c>
-      <c r="C49" s="56"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="56"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="56"/>
-      <c r="I49" s="56"/>
-      <c r="J49" s="56"/>
-      <c r="K49" s="56"/>
-      <c r="L49" s="56"/>
+      <c r="B49" s="62" t="s">
+        <v>273</v>
+      </c>
+      <c r="C49" s="58"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="58"/>
+      <c r="H49" s="58"/>
+      <c r="I49" s="58"/>
+      <c r="J49" s="58"/>
+      <c r="K49" s="58"/>
+      <c r="L49" s="58"/>
     </row>
     <row r="51" spans="1:12" ht="55.5" customHeight="1">
       <c r="A51" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B51" s="75" t="s">
         <v>297</v>
       </c>
-      <c r="B51" s="65" t="s">
-        <v>298</v>
-      </c>
-      <c r="C51" s="65"/>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
-      <c r="F51" s="65"/>
-      <c r="G51" s="65"/>
-      <c r="H51" s="65"/>
-      <c r="I51" s="65"/>
-      <c r="J51" s="65"/>
-      <c r="K51" s="65"/>
+      <c r="C51" s="75"/>
+      <c r="D51" s="75"/>
+      <c r="E51" s="75"/>
+      <c r="F51" s="75"/>
+      <c r="G51" s="75"/>
+      <c r="H51" s="75"/>
+      <c r="I51" s="75"/>
+      <c r="J51" s="75"/>
+      <c r="K51" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="B49:L49"/>
+    <mergeCell ref="B51:K51"/>
+    <mergeCell ref="B13:L13"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="A12:A21"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="D21:N21"/>
+    <mergeCell ref="C24:O24"/>
+    <mergeCell ref="C25:O25"/>
+    <mergeCell ref="C26:O26"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="D18:N18"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="D19:O19"/>
+    <mergeCell ref="C34:I34"/>
     <mergeCell ref="A23:A39"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C33:H33"/>
@@ -3925,34 +3972,6 @@
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:G29"/>
     <mergeCell ref="C30:G30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="D18:N18"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="D19:O19"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="D21:N21"/>
-    <mergeCell ref="C24:O24"/>
-    <mergeCell ref="C25:O25"/>
-    <mergeCell ref="C26:O26"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B49:L49"/>
-    <mergeCell ref="B51:K51"/>
-    <mergeCell ref="B13:L13"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B10:J10"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="A12:A21"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3969,110 +3988,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="80" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1">
+      <c r="A2" s="79" t="s">
+        <v>283</v>
+      </c>
+      <c r="B2" s="79"/>
+      <c r="C2" s="45" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-    </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1">
-      <c r="A2" s="75" t="s">
-        <v>284</v>
-      </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="44" t="s">
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+    </row>
+    <row r="3" spans="1:12" ht="34.5" customHeight="1">
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="62" t="s">
         <v>277</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-    </row>
-    <row r="3" spans="1:12" ht="34.5" customHeight="1">
-      <c r="A3" s="75"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="57" t="s">
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
+    </row>
+    <row r="5" spans="1:12" ht="38.25" customHeight="1">
+      <c r="A5" s="79"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="75"/>
-      <c r="B4" s="75"/>
-    </row>
-    <row r="5" spans="1:12" ht="38.25" customHeight="1">
-      <c r="A5" s="75"/>
-      <c r="B5" s="75"/>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="62" t="s">
         <v>279</v>
       </c>
-      <c r="D5" s="57" t="s">
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+    </row>
+    <row r="6" spans="1:12" s="22" customFormat="1" ht="83.25" customHeight="1">
+      <c r="A6" s="79"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-    </row>
-    <row r="6" spans="1:12" s="22" customFormat="1" ht="83.25" customHeight="1">
-      <c r="A6" s="75"/>
-      <c r="B6" s="75"/>
-      <c r="C6" s="40" t="s">
+      <c r="D6" s="62" t="s">
         <v>281</v>
       </c>
-      <c r="D6" s="57" t="s">
-        <v>282</v>
-      </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="56"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
     </row>
     <row r="7" spans="1:12" s="22" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="75"/>
-      <c r="B7" s="75"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="57" t="s">
-        <v>289</v>
-      </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
+      <c r="A7" s="79"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="62" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="39"/>
@@ -4089,73 +4108,78 @@
       <c r="L8" s="39"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="40" t="s">
-        <v>283</v>
-      </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="44" t="s">
-        <v>288</v>
-      </c>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
+      <c r="A9" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="B9" s="42"/>
+      <c r="C9" s="45" t="s">
+        <v>287</v>
+      </c>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
     </row>
     <row r="10" spans="1:12" ht="41.25" customHeight="1">
-      <c r="A10" s="40"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="57" t="s">
+      <c r="A10" s="42"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="62" t="s">
+        <v>284</v>
+      </c>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="58"/>
+      <c r="K10" s="58"/>
+      <c r="L10" s="58"/>
+    </row>
+    <row r="11" spans="1:12" ht="19.5" customHeight="1">
+      <c r="A11" s="42"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="58" t="s">
         <v>285</v>
       </c>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-    </row>
-    <row r="11" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="56" t="s">
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
+      <c r="K11" s="58"/>
+      <c r="L11" s="58"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="42"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="45" t="s">
         <v>286</v>
       </c>
-      <c r="D11" s="56"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="56"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="56"/>
-      <c r="L11" s="56"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="40"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="44" t="s">
-        <v>287</v>
-      </c>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="C12:L12"/>
+    <mergeCell ref="A9:B12"/>
     <mergeCell ref="D7:L7"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="A2:B7"/>
@@ -4164,11 +4188,6 @@
     <mergeCell ref="C3:L3"/>
     <mergeCell ref="D5:L5"/>
     <mergeCell ref="D6:L6"/>
-    <mergeCell ref="C10:L10"/>
-    <mergeCell ref="C9:L9"/>
-    <mergeCell ref="C11:L11"/>
-    <mergeCell ref="C12:L12"/>
-    <mergeCell ref="A9:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4187,119 +4206,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="49" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+    </row>
+    <row r="3" spans="1:9" ht="20.25" customHeight="1">
+      <c r="B3" s="58" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-    </row>
-    <row r="3" spans="1:9" ht="20.25" customHeight="1">
-      <c r="B3" s="56" t="s">
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="48" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+    </row>
+    <row r="5" spans="1:9" ht="21" customHeight="1">
+      <c r="B5" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-    </row>
-    <row r="5" spans="1:9" ht="21" customHeight="1">
-      <c r="B5" s="56" t="s">
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="81" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="44" t="s">
-        <v>181</v>
-      </c>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="B11" s="49"/>
+      <c r="B11" s="44"/>
     </row>
     <row r="12" spans="1:9">
       <c r="B12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="B13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="40.5" customHeight="1">
       <c r="A15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" s="64" t="s">
         <v>255</v>
       </c>
-      <c r="B15" s="63" t="s">
-        <v>256</v>
-      </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4320,7 +4339,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3177FA43-C9E8-4CC7-B84D-76C751FF5B02}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="85" customWidth="1"/>
@@ -4330,74 +4349,82 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" t="s">
         <v>141</v>
-      </c>
-      <c r="B2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" t="s">
         <v>199</v>
-      </c>
-      <c r="B3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" t="s">
         <v>203</v>
-      </c>
-      <c r="C4" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5" t="s">
         <v>207</v>
-      </c>
-      <c r="C5" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" t="s">
         <v>211</v>
-      </c>
-      <c r="C6" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" t="s">
         <v>209</v>
-      </c>
-      <c r="C7" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B8" t="s">
         <v>291</v>
-      </c>
-      <c r="B8" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" t="s">
         <v>305</v>
       </c>
-      <c r="B9" t="s">
-        <v>306</v>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -4419,81 +4446,81 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="44.25" customHeight="1">
       <c r="A3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="62" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="B4" s="42" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="B4" s="40" t="s">
+      <c r="C4" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="B5" s="42"/>
+      <c r="C5" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="B5" s="40"/>
-      <c r="C5" s="44" t="s">
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="B6" s="42"/>
+      <c r="C6" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="B6" s="40"/>
-      <c r="C6" s="44" t="s">
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7" s="42"/>
+      <c r="C7" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="B7" s="40"/>
-      <c r="C7" s="44" t="s">
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="B8" s="42"/>
+      <c r="C8" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="B8" s="40"/>
-      <c r="C8" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4524,115 +4551,115 @@
   <sheetData>
     <row r="1" spans="1:15" ht="36" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="78" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
+      <c r="C1" s="82" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="60" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
+      <c r="C3" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="44" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4661,61 +4688,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
     </row>
     <row r="6" spans="1:13">
       <c r="B6" s="6"/>
@@ -4727,64 +4754,64 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
+        <v>20</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="B10" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="B10" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="46"/>
       <c r="C14" s="46"/>
@@ -4793,87 +4820,87 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
+        <v>30</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
     </row>
     <row r="17" spans="1:9" ht="39.75" customHeight="1">
       <c r="A17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="48" t="s">
+      <c r="B19" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="49" t="s">
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="43"/>
+      <c r="B20" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="48"/>
-      <c r="B20" s="49" t="s">
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="48" t="s">
+      <c r="B22" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="49" t="s">
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="43"/>
+      <c r="B23" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="48"/>
-      <c r="B23" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="46"/>
       <c r="C25" s="46"/>
@@ -4884,26 +4911,37 @@
     </row>
     <row r="27" spans="1:9" ht="30">
       <c r="A27" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
     </row>
     <row r="29" spans="1:9">
       <c r="B29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B12:M12"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B10:H10"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="B23:I23"/>
@@ -4912,17 +4950,6 @@
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B12:M12"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B9:H9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -4942,156 +4969,156 @@
   <sheetData>
     <row r="2" spans="1:2" ht="75">
       <c r="B2" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30">
       <c r="A4" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30">
       <c r="B6" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="65.25" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="45">
       <c r="A10" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45">
       <c r="A12" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="51.75">
       <c r="A16" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="45">
       <c r="B18" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="30">
       <c r="B20" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="45">
       <c r="B22" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="45">
       <c r="B24" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="90">
       <c r="B26" s="20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="45">
       <c r="B27" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="45">
       <c r="B29" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="45">
       <c r="B31" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="30">
       <c r="B33" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="75">
       <c r="B35" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="30">
       <c r="B37" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="B41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="30">
       <c r="B43" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="B45" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B47" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30">
       <c r="A49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="90">
       <c r="B51" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="45">
       <c r="B53" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -5115,78 +5142,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.5">
-      <c r="A1" s="53" t="s">
-        <v>247</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="A1" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="50" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="51"/>
+      <c r="A2" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="53"/>
       <c r="C2" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D2" s="26"/>
       <c r="E2" s="26"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="51"/>
-      <c r="B3" s="51"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="27" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D3" s="26"/>
       <c r="E3" s="26"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
       <c r="C4" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
+      <c r="A5" s="53"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="26"/>
     </row>
     <row r="6" spans="1:5" ht="30">
-      <c r="A6" s="51"/>
-      <c r="B6" s="51"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="53"/>
       <c r="C6" s="27" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="51"/>
-      <c r="B7" s="51"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="53"/>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="53"/>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="30">
-      <c r="A9" s="51"/>
-      <c r="B9" s="51"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="27" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="26"/>
@@ -5199,30 +5226,30 @@
       <c r="E10" s="31"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="B11" s="52"/>
+      <c r="A11" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="54"/>
       <c r="C11" s="26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="52"/>
-      <c r="B12" s="52"/>
+      <c r="A12" s="54"/>
+      <c r="B12" s="54"/>
       <c r="C12" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="52"/>
-      <c r="B13" s="52"/>
+      <c r="A13" s="54"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="26" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="26"/>
@@ -5235,69 +5262,69 @@
       <c r="E14" s="31"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" s="54"/>
+      <c r="C15" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="32" t="s">
+      <c r="D15" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D15" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="32" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="45">
+      <c r="A16" s="54"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="26" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="45">
-      <c r="A16" s="52"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="26" t="s">
+      <c r="D16" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>242</v>
-      </c>
       <c r="E16" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="52"/>
-      <c r="B17" s="52"/>
+      <c r="A17" s="54"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="26"/>
       <c r="D17" s="26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E17" s="26"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="52"/>
-      <c r="B18" s="52"/>
+      <c r="A18" s="54"/>
+      <c r="B18" s="54"/>
       <c r="C18" s="26"/>
       <c r="D18" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="52"/>
-      <c r="B19" s="52"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="26"/>
       <c r="D19" s="26"/>
       <c r="E19" s="26"/>
     </row>
     <row r="20" spans="1:5" ht="30">
-      <c r="A20" s="52"/>
-      <c r="B20" s="52"/>
+      <c r="A20" s="54"/>
+      <c r="B20" s="54"/>
       <c r="C20" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="E20" s="27" t="s">
         <v>245</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -5324,17 +5351,17 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="2:2" ht="45">
       <c r="B3" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="45">
       <c r="B5" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -5354,57 +5381,57 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" t="s">
         <v>221</v>
-      </c>
-      <c r="B1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45">
       <c r="A2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" t="s">
         <v>224</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="20" t="s">
         <v>225</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" t="s">
         <v>299</v>
-      </c>
-      <c r="B3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C3" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30">
       <c r="A4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>301</v>
-      </c>
-      <c r="B4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30">
       <c r="A5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>303</v>
-      </c>
-      <c r="B5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -5422,122 +5449,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30.75" customHeight="1">
-      <c r="A1" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="A1" s="57" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
     </row>
     <row r="3" spans="1:13">
       <c r="B3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="58" t="s">
         <v>157</v>
       </c>
-      <c r="C3" s="56" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
     </row>
     <row r="4" spans="1:13">
       <c r="B4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="44" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" t="s">
         <v>161</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="45" t="s">
         <v>162</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>163</v>
-      </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
     </row>
     <row r="7" spans="1:13">
       <c r="B7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
     </row>
     <row r="8" spans="1:13">
       <c r="B8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5564,303 +5591,295 @@
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="79" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A1" s="81" t="s">
-        <v>324</v>
-      </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
+    <row r="1" spans="1:16" s="40" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A1" s="60" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
       <c r="M1" s="20"/>
       <c r="N1" s="20"/>
       <c r="O1" s="20"/>
       <c r="P1" s="20"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="56" t="s">
+      <c r="A2" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="42"/>
+      <c r="B3" s="45" t="s">
         <v>307</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="40"/>
-      <c r="B3" s="44" t="s">
-        <v>308</v>
-      </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="40"/>
-      <c r="B4" s="56" t="s">
+      <c r="A4" s="42"/>
+      <c r="B4" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="42"/>
+      <c r="B5" s="58" t="s">
         <v>311</v>
       </c>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="40"/>
-      <c r="B5" s="56" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="82"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="82"/>
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
     </row>
     <row r="7" spans="1:16" ht="43.5" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B7" s="62" t="s">
         <v>309</v>
       </c>
-      <c r="B7" s="57" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="82"/>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="82"/>
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
     </row>
     <row r="9" spans="1:16" ht="38.25" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="59" t="s">
+        <v>312</v>
+      </c>
+      <c r="B9" s="62" t="s">
         <v>313</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+    </row>
+    <row r="10" spans="1:16" ht="20.25" customHeight="1">
+      <c r="A10" s="59"/>
+      <c r="B10" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-    </row>
-    <row r="10" spans="1:16" ht="20.25" customHeight="1">
-      <c r="A10" s="71"/>
-      <c r="B10" s="56" t="s">
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="58"/>
+      <c r="K10" s="58"/>
+    </row>
+    <row r="11" spans="1:16" ht="41.25" customHeight="1">
+      <c r="A11" s="59"/>
+      <c r="B11" s="62" t="s">
         <v>315</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-    </row>
-    <row r="11" spans="1:16" ht="41.25" customHeight="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="57" t="s">
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+    </row>
+    <row r="12" spans="1:16" ht="21" customHeight="1">
+      <c r="A12" s="59"/>
+      <c r="B12" s="58" t="s">
         <v>316</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
-    </row>
-    <row r="12" spans="1:16" ht="21" customHeight="1">
-      <c r="A12" s="71"/>
-      <c r="B12" s="56" t="s">
-        <v>317</v>
-      </c>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="56"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="58"/>
+      <c r="K12" s="58"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="82"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
+      <c r="A13" s="41"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
     </row>
     <row r="14" spans="1:16" ht="43.5" customHeight="1">
       <c r="A14" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B14" s="62" t="s">
         <v>318</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="41"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+    </row>
+    <row r="16" spans="1:16" ht="30" customHeight="1">
+      <c r="A16" s="59" t="s">
         <v>319</v>
       </c>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
-      <c r="L14" s="57"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="82"/>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="82"/>
-      <c r="H15" s="82"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="82"/>
-    </row>
-    <row r="16" spans="1:16" ht="30" customHeight="1">
-      <c r="A16" s="71" t="s">
+      <c r="B16" s="58" t="s">
         <v>320</v>
       </c>
-      <c r="B16" s="56" t="s">
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+    </row>
+    <row r="17" spans="1:20" ht="30" customHeight="1">
+      <c r="A17" s="59"/>
+      <c r="B17" s="62" t="s">
         <v>321</v>
       </c>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="56"/>
-    </row>
-    <row r="17" spans="1:20" ht="30" customHeight="1">
-      <c r="A17" s="71"/>
-      <c r="B17" s="57" t="s">
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" s="59"/>
+      <c r="B18" s="43" t="s">
         <v>322</v>
       </c>
-      <c r="C17" s="57"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="57"/>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="71"/>
-      <c r="B18" s="48" t="s">
-        <v>323</v>
-      </c>
-      <c r="C18" s="48"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="48"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
     </row>
     <row r="21" spans="1:20">
-      <c r="J21" s="57"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="57"/>
-      <c r="P21" s="57"/>
-      <c r="Q21" s="57"/>
-      <c r="R21" s="57"/>
-      <c r="S21" s="57"/>
-      <c r="T21" s="57"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="62"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="62"/>
+      <c r="O21" s="62"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="62"/>
+      <c r="S21" s="62"/>
+      <c r="T21" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B9:K9"/>
-    <mergeCell ref="B10:K10"/>
-    <mergeCell ref="B11:K11"/>
-    <mergeCell ref="B12:K12"/>
-    <mergeCell ref="A9:A12"/>
     <mergeCell ref="J21:T21"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:K3"/>
@@ -5871,6 +5890,14 @@
     <mergeCell ref="B16:K16"/>
     <mergeCell ref="B17:K17"/>
     <mergeCell ref="B18:K18"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="B11:K11"/>
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="A9:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5893,105 +5920,105 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="B2" s="37" t="s">
         <v>257</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="C2" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="D2" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="E2" s="37" t="s">
         <v>260</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="F2" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="F2" s="37" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="45">
+      <c r="A3" s="42"/>
+      <c r="B3" s="37" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="45">
-      <c r="A3" s="40"/>
-      <c r="B3" s="37" t="s">
+      <c r="C3" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="D3" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="E3" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="F3" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="F3" s="25" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="30">
+      <c r="A4" s="42"/>
+      <c r="B4" s="37" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="30">
-      <c r="A4" s="40"/>
-      <c r="B4" s="37" t="s">
+      <c r="C4" s="33" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="D4" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="E4" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="F4" s="25" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30">
+      <c r="A5" s="42"/>
+      <c r="B5" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="30">
-      <c r="A5" s="40"/>
-      <c r="B5" s="37" t="s">
+      <c r="C5" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="42"/>
+      <c r="B6" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C6" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="D5" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>271</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="40"/>
-      <c r="B6" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>270</v>
-      </c>
       <c r="D6" s="35" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="41.25" customHeight="1">
-      <c r="B8" s="57" t="s">
-        <v>290</v>
-      </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
+      <c r="B8" s="62" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Certifications/Snowpro Core/SnowProCore.xlsx
+++ b/Certifications/Snowpro Core/SnowProCore.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dialogsl-my.sharepoint.com/personal/lahiru_nuwan_dialog_lk/Documents/Desktop/Certifications/Snowpro Core/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{1C6F829D-7B29-4D13-B004-2A9C59841126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACA6BE47-0C2D-4EF4-A204-5A24DE393676}"/>
+  <xr:revisionPtr revIDLastSave="262" documentId="13_ncr:1_{1C6F829D-7B29-4D13-B004-2A9C59841126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD377BB8-896F-47C9-8C31-9994EA72AA72}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1020" windowWidth="29040" windowHeight="15840" xr2:uid="{A1DD3791-2758-4015-950E-6866E350408A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="13" activeTab="14" xr2:uid="{A1DD3791-2758-4015-950E-6866E350408A}"/>
   </bookViews>
   <sheets>
     <sheet name="SF Editions" sheetId="2" r:id="rId1"/>
@@ -21,14 +21,15 @@
     <sheet name="Supportive Views and Functions" sheetId="13" r:id="rId6"/>
     <sheet name="Micro-partitions &amp; Data Cluster" sheetId="10" r:id="rId7"/>
     <sheet name="Network Policy" sheetId="15" r:id="rId8"/>
-    <sheet name="Snowflake Tables" sheetId="16" r:id="rId9"/>
-    <sheet name="Secure Data Sharing" sheetId="6" r:id="rId10"/>
-    <sheet name="Data Loading-unloading" sheetId="7" r:id="rId11"/>
-    <sheet name="Data Access Policies" sheetId="17" r:id="rId12"/>
-    <sheet name="Access Control" sheetId="11" r:id="rId13"/>
-    <sheet name="Questions" sheetId="8" r:id="rId14"/>
-    <sheet name="Streams" sheetId="9" r:id="rId15"/>
-    <sheet name="Fail-Safe" sheetId="4" r:id="rId16"/>
+    <sheet name="QAS" sheetId="18" r:id="rId9"/>
+    <sheet name="Snowflake Tables and Views" sheetId="16" r:id="rId10"/>
+    <sheet name="Secure Data Sharing" sheetId="6" r:id="rId11"/>
+    <sheet name="Data Loading-unloading" sheetId="7" r:id="rId12"/>
+    <sheet name="Data Access Policies" sheetId="17" r:id="rId13"/>
+    <sheet name="Access Control" sheetId="11" r:id="rId14"/>
+    <sheet name="Questions" sheetId="8" r:id="rId15"/>
+    <sheet name="Streams" sheetId="9" r:id="rId16"/>
+    <sheet name="Fail-Safe" sheetId="4" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="382">
   <si>
     <t>Feature</t>
   </si>
@@ -72,9 +73,6 @@
   </si>
   <si>
     <t>Automatic Scaling</t>
-  </si>
-  <si>
-    <t>Failover &amp; Replication</t>
   </si>
   <si>
     <t>Multi-cluster Warehouses</t>
@@ -1897,12 +1895,240 @@
   <si>
     <t xml:space="preserve">Failover and failback and Redirecting client connections </t>
   </si>
+  <si>
+    <t>Query Acceleration Service</t>
+  </si>
+  <si>
+    <t>QAS can accelerate parts of the query workload in a warehouse</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">improve overall warehouse performance by reducing the impact of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>outlier queries</t>
+    </r>
+  </si>
+  <si>
+    <t>does this by offloading portions of the query processing work to shared compute 
+resources that are provided by the service</t>
+  </si>
+  <si>
+    <t>Ad hoc analytics</t>
+  </si>
+  <si>
+    <t>Workloads with unpredictable data volume per query</t>
+  </si>
+  <si>
+    <t>Queries with large scans and selective filters.</t>
+  </si>
+  <si>
+    <t>Ideal workloads</t>
+  </si>
+  <si>
+    <t>Check Eligibility</t>
+  </si>
+  <si>
+    <t>Tool/Method</t>
+  </si>
+  <si>
+    <t>Identify eligible queries/warehouses</t>
+  </si>
+  <si>
+    <t>Assess specific query eligibility</t>
+  </si>
+  <si>
+    <r>
+      <t>QUERY_ACCELERATION_ELIGIBLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> view</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SYSTEM$ESTIMATE_QUERY_ACCELERATION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> function</t>
+    </r>
+  </si>
+  <si>
+    <t>Common Reasons
+ for Ineligibility</t>
+  </si>
+  <si>
+    <t>Low filter selectivity / high GROUP BY cardinality – Limits effectiveness</t>
+  </si>
+  <si>
+    <t>LIMIT without ORDER BY – Not eligible for acceleration.</t>
+  </si>
+  <si>
+    <t>Nondeterministic functions – Usage of functions like SEQ or RANDOM</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Too few partitions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – Insufficient partitions reduce acceleration benefits.</t>
+    </r>
+  </si>
+  <si>
+    <t>Supported SQL 
+Commands</t>
+  </si>
+  <si>
+    <t>The query acceleration service supports the following SQL commands:</t>
+  </si>
+  <si>
+    <t>SELECT</t>
+  </si>
+  <si>
+    <t>INSERT</t>
+  </si>
+  <si>
+    <t>CREATE TABLE AS SELECT (CTAS)</t>
+  </si>
+  <si>
+    <t>COPY INTO &lt;table&gt;</t>
+  </si>
+  <si>
+    <t>Scale Factor</t>
+  </si>
+  <si>
+    <t>Controls cost by setting an upper bound on leased compute resources</t>
+  </si>
+  <si>
+    <t>Acts as a multiplier on warehouse size and cost</t>
+  </si>
+  <si>
+    <t>Example - Scale factor 5 on a medium warehouse (4 credits/hour) → up to 20 extra credits/hour</t>
+  </si>
+  <si>
+    <t>Billed per second only when in use; separate from warehouse billing</t>
+  </si>
+  <si>
+    <t>Default Value - 8</t>
+  </si>
+  <si>
+    <t>if 0 -  No upper bound; uses as many resources as needed and available</t>
+  </si>
+  <si>
+    <t>dedicated metadata store</t>
+  </si>
+  <si>
+    <t>When WAIT_FOR_COMPLETION = TRUE is set, the command will wait and not return until the process of resizing the 
+warehouse is fully completed</t>
+  </si>
+  <si>
+    <t>Secure View</t>
+  </si>
+  <si>
+    <t>Secure views may run more slowly than non-secure views</t>
+  </si>
+  <si>
+    <t>support for periodic rekeying of encrypted data</t>
+  </si>
+  <si>
+    <t>View</t>
+  </si>
+  <si>
+    <t>ACCOUNT_USAGE.METERING_HISTORY</t>
+  </si>
+  <si>
+    <t>provides detailed information about the hourly credit consumption of an account. It allows you to monitor credit usage across virtual 
+warehouses, cloud services, and other resources over time.</t>
+  </si>
+  <si>
+    <t>Account Usage.Access History View</t>
+  </si>
+  <si>
+    <t>Snowflake implements automatic key rotation every 30 days to enhance security</t>
+  </si>
+  <si>
+    <t>SYSTEM$IS_LISTING_PURCHASED</t>
+  </si>
+  <si>
+    <t>enables access control by checking if a customer has purchased the data listing, allowing data to be displayed only to paying customers</t>
+  </si>
+  <si>
+    <t>Which SQL command can be used to see the CREATE definition of a masking policy?</t>
+  </si>
+  <si>
+    <t>GET_DDL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The default value for DATA_RETENTION_TIME_IN_DAYS is 1 for all editions of Snowflake.
+</t>
+  </si>
+  <si>
+    <t>Data consumers cannot re-share shared database objects.</t>
+  </si>
+  <si>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>User defined functions can  be executed in the context of another statement</t>
+  </si>
+  <si>
+    <t>A data provider can add an unlimited number of database objects to a SHARE object in Snowflake;</t>
+  </si>
+  <si>
+    <t>What is the recommended maximum number of columns (or expressions) defined per clustering key?</t>
+  </si>
+  <si>
+    <t>3 or 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which system function is called to retrieve clustering metadata for a column or columns? </t>
+  </si>
+  <si>
+    <t>system$clustering_information</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2019,6 +2245,13 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2161,7 +2394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2240,6 +2473,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2303,6 +2537,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2324,19 +2564,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2360,6 +2600,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -2699,7 +2942,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2709,14 +2952,14 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -2724,18 +2967,21 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="42"/>
+      <c r="A3" s="43"/>
       <c r="B3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="42"/>
+      <c r="A4" s="43"/>
+      <c r="B4" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="42"/>
+      <c r="A5" s="43"/>
       <c r="B5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2743,96 +2989,109 @@
       <c r="B6" s="5"/>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="43"/>
+      <c r="B8" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="43"/>
+      <c r="B9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="43"/>
+      <c r="B10" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="43"/>
+      <c r="B11" s="23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="43"/>
+      <c r="B14" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="43"/>
+      <c r="B15" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="42"/>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="42"/>
-      <c r="B9" t="s">
+    <row r="16" spans="1:2">
+      <c r="A16" s="43"/>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="43"/>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="43"/>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="43"/>
+      <c r="B21" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="42"/>
-      <c r="B10" s="23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="42"/>
-      <c r="B13" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="42"/>
-      <c r="B14" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="42"/>
-      <c r="B15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="42"/>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="42"/>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="B20" t="s">
-        <v>217</v>
+    <row r="22" spans="1:2">
+      <c r="A22" s="43"/>
+      <c r="B22" t="s">
+        <v>359</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A18:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2843,11 +3102,150 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055368DB-E282-4263-B8BF-74FF1A138266}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A2:F13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="45">
+      <c r="A3" s="43"/>
+      <c r="B3" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30">
+      <c r="A4" s="43"/>
+      <c r="B4" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30">
+      <c r="A5" s="43"/>
+      <c r="B5" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="43"/>
+      <c r="B6" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="41.25" customHeight="1">
+      <c r="B8" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>361</v>
+      </c>
+      <c r="B11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" t="s">
+        <v>376</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B8:F8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E21AF3-8ECD-4AEA-A595-39E544DE641B}">
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2855,98 +3253,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+    </row>
+    <row r="2" spans="1:13" ht="36.75" customHeight="1">
+      <c r="A2" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-    </row>
-    <row r="2" spans="1:13" ht="36.75" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="42" t="s">
+      <c r="B4" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="70"/>
+      <c r="B5" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="67"/>
-      <c r="B5" s="45" t="s">
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="70"/>
+      <c r="B6" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="67"/>
-      <c r="B6" s="45" t="s">
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+    </row>
+    <row r="7" spans="1:13" ht="16.5" customHeight="1">
+      <c r="A7" s="70"/>
+      <c r="B7" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-    </row>
-    <row r="7" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A7" s="67"/>
-      <c r="B7" s="64" t="s">
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="70"/>
+      <c r="B8" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="67"/>
-      <c r="B8" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="13"/>
@@ -2958,324 +3356,348 @@
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="42" t="s">
+    <row r="10" spans="1:13" s="87" customFormat="1">
+      <c r="A10" s="86" t="s">
+        <v>375</v>
+      </c>
+      <c r="B10" s="87" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="87" customFormat="1">
+      <c r="A11" s="86"/>
+      <c r="B11" s="87" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="43"/>
+      <c r="B14" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="43"/>
+      <c r="B15" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+    </row>
+    <row r="17" spans="1:9" ht="45" customHeight="1">
+      <c r="A17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="42"/>
-      <c r="B11" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="42"/>
-      <c r="B12" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:13" ht="45" customHeight="1">
-      <c r="A14" s="3" t="s">
+      <c r="B17" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="62" t="s">
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="42" t="s">
+      <c r="B19" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="43"/>
+      <c r="B20" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+    </row>
+    <row r="21" spans="1:9" ht="88.5" customHeight="1">
+      <c r="A21" s="43"/>
+      <c r="B21" s="66" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="66"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="66"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="43"/>
+      <c r="B22" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="42"/>
-      <c r="B17" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-    </row>
-    <row r="18" spans="1:9" ht="88.5" customHeight="1">
-      <c r="A18" s="42"/>
-      <c r="B18" s="63" t="s">
+    <row r="23" spans="1:9" ht="45" customHeight="1">
+      <c r="A23" s="43"/>
+      <c r="B23" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="43"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="43"/>
+      <c r="B25" s="14" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="43"/>
+      <c r="B26" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+    </row>
+    <row r="27" spans="1:9" ht="91.5" customHeight="1">
+      <c r="A27" s="43"/>
+      <c r="B27" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="43"/>
+      <c r="B28" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="60" customHeight="1">
+      <c r="A29" s="43"/>
+      <c r="B29" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="42"/>
-      <c r="B19" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="45" customHeight="1">
-      <c r="A20" s="42"/>
-      <c r="B20" s="63" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="42"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="42"/>
-      <c r="B22" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="42"/>
-      <c r="B23" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-    </row>
-    <row r="24" spans="1:9" ht="91.5" customHeight="1">
-      <c r="A24" s="42"/>
-      <c r="B24" s="64" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="42"/>
-      <c r="B25" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="60" customHeight="1">
-      <c r="A26" s="42"/>
-      <c r="B26" s="64" t="s">
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" spans="1:9" ht="39" customHeight="1">
+      <c r="B31" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-    </row>
-    <row r="28" spans="1:9" ht="39" customHeight="1">
-      <c r="B28" s="64" t="s">
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="64"/>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="64"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="42" t="s">
+      <c r="B33" t="s">
         <v>80</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C33" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="45" t="s">
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="46"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="43"/>
+      <c r="B34" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="42"/>
-      <c r="B31" t="s">
+      <c r="C34" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="45" t="s">
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="43"/>
+      <c r="B35" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="42"/>
-      <c r="B32" t="s">
+      <c r="C35" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="45" t="s">
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="43"/>
+      <c r="B36" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="42"/>
-      <c r="B33" t="s">
+      <c r="C36" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-    </row>
-    <row r="35" spans="1:10" ht="45.75" customHeight="1">
-      <c r="B35" s="68" t="s">
-        <v>192</v>
-      </c>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+    </row>
+    <row r="38" spans="1:10" ht="45.75" customHeight="1">
+      <c r="B38" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="C38" s="72"/>
+      <c r="D38" s="72"/>
+      <c r="E38" s="72"/>
+      <c r="F38" s="72"/>
+      <c r="G38" s="72"/>
+      <c r="H38" s="72"/>
+      <c r="I38" s="72"/>
+      <c r="J38" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="B38:J38"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="C36:I36"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B8:H8"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="A33:A36"/>
     <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="A16:A26"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="C30:I30"/>
-    <mergeCell ref="C31:I31"/>
-    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="A19:A29"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="C35:I35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E11F3A5-7945-48AC-9F97-7B0CC4D0FA3A}">
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
@@ -3289,143 +3711,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="76" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
+      <c r="A1" s="79" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="45" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
+        <v>44</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
     </row>
     <row r="6" spans="1:13" ht="42.75" customHeight="1">
       <c r="A6" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
+        <v>98</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="81" t="s">
         <v>100</v>
       </c>
-      <c r="B9" s="78" t="s">
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="81"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="B10" s="81" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="78"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="B10" s="78" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="78"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="13"/>
@@ -3443,43 +3865,43 @@
       <c r="M11" s="13"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="42"/>
-      <c r="B13" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
+      <c r="A13" s="43"/>
+      <c r="B13" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="42"/>
+      <c r="A14" s="43"/>
       <c r="B14" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -3493,91 +3915,91 @@
       <c r="L14" s="6"/>
     </row>
     <row r="15" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A15" s="42"/>
-      <c r="C15" s="62" t="s">
+      <c r="A15" s="43"/>
+      <c r="C15" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="8"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="43"/>
+      <c r="B16" s="17" t="s">
         <v>107</v>
-      </c>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="62"/>
-      <c r="L15" s="62"/>
-      <c r="M15" s="8"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="42"/>
-      <c r="B16" s="17" t="s">
-        <v>108</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="42"/>
-      <c r="C17" s="74" t="s">
+      <c r="A17" s="43"/>
+      <c r="C17" s="75" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="75"/>
+    </row>
+    <row r="18" spans="1:15" ht="45.75" customHeight="1">
+      <c r="A18" s="43"/>
+      <c r="D18" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="74"/>
-    </row>
-    <row r="18" spans="1:15" ht="45.75" customHeight="1">
-      <c r="A18" s="42"/>
-      <c r="D18" s="62" t="s">
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="63"/>
+    </row>
+    <row r="19" spans="1:15" ht="20.25" customHeight="1">
+      <c r="A19" s="43"/>
+      <c r="D19" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="63"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="43"/>
+      <c r="C20" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="62"/>
-    </row>
-    <row r="19" spans="1:15" ht="20.25" customHeight="1">
-      <c r="A19" s="42"/>
-      <c r="D19" s="62" t="s">
+      <c r="D20" s="75"/>
+    </row>
+    <row r="21" spans="1:15" ht="27" customHeight="1">
+      <c r="A21" s="43"/>
+      <c r="D21" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="62"/>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="42"/>
-      <c r="C20" s="74" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" s="74"/>
-    </row>
-    <row r="21" spans="1:15" ht="27" customHeight="1">
-      <c r="A21" s="42"/>
-      <c r="D21" s="58" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="59"/>
+      <c r="N21" s="59"/>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="13"/>
@@ -3597,192 +4019,192 @@
       <c r="O22" s="13"/>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="59" t="s">
+      <c r="A23" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="77" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="73" t="s">
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="60"/>
+      <c r="C24" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="59"/>
-      <c r="C24" s="45" t="s">
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
+      <c r="O24" s="46"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="60"/>
+      <c r="C25" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
-      <c r="M24" s="45"/>
-      <c r="N24" s="45"/>
-      <c r="O24" s="45"/>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="59"/>
-      <c r="C25" s="45" t="s">
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="60"/>
+      <c r="C26" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="45"/>
-      <c r="M25" s="45"/>
-      <c r="N25" s="45"/>
-      <c r="O25" s="45"/>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="59"/>
-      <c r="C26" s="45" t="s">
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="60"/>
+      <c r="B27" s="77" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
-      <c r="O26" s="45"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="59"/>
-      <c r="B27" s="73" t="s">
+      <c r="C27" s="77"/>
+      <c r="D27" s="77"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="60"/>
+      <c r="C28" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" s="59"/>
-      <c r="C28" s="45" t="s">
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="60"/>
+      <c r="C29" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-    </row>
-    <row r="29" spans="1:15">
-      <c r="A29" s="59"/>
-      <c r="C29" s="45" t="s">
+      <c r="D29" s="46"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="60"/>
+      <c r="C30" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="A30" s="59"/>
-      <c r="C30" s="45" t="s">
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="60"/>
+      <c r="B31" s="77" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="A31" s="59"/>
-      <c r="B31" s="73" t="s">
+      <c r="C31" s="77"/>
+      <c r="D31" s="77"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="60"/>
+      <c r="C32" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="A32" s="59"/>
-      <c r="C32" s="70" t="s">
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="60"/>
+      <c r="C33" s="76" t="s">
         <v>125</v>
       </c>
-      <c r="D32" s="70"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-    </row>
-    <row r="33" spans="1:16">
-      <c r="A33" s="59"/>
-      <c r="C33" s="70" t="s">
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="60"/>
+      <c r="C34" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="A34" s="59"/>
-      <c r="C34" s="45" t="s">
+      <c r="D34" s="46"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="60"/>
+      <c r="B35" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="A35" s="59"/>
-      <c r="B35" s="18" t="s">
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="60"/>
+      <c r="C36" s="46" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="59"/>
-      <c r="C36" s="45" t="s">
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="60"/>
+      <c r="C37" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="59"/>
-      <c r="C37" s="45" t="s">
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="46"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="60"/>
+      <c r="C38" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-    </row>
-    <row r="38" spans="1:16">
-      <c r="A38" s="59"/>
-      <c r="C38" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="46"/>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="59"/>
+      <c r="A39" s="60"/>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="13"/>
@@ -3802,133 +4224,132 @@
       <c r="O40" s="13"/>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="B41" s="71" t="s">
+      <c r="A41" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" s="73" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="73"/>
+    </row>
+    <row r="42" spans="1:16" ht="40.5" customHeight="1">
+      <c r="A42" s="43"/>
+      <c r="C42" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="C41" s="71"/>
-    </row>
-    <row r="42" spans="1:16" ht="40.5" customHeight="1">
-      <c r="A42" s="42"/>
-      <c r="C42" s="72" t="s">
+      <c r="D42" s="74"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="74"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="74"/>
+      <c r="L42" s="74"/>
+      <c r="M42" s="74"/>
+      <c r="N42" s="74"/>
+      <c r="O42" s="74"/>
+      <c r="P42" s="74"/>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="43"/>
+      <c r="B43" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="D42" s="72"/>
-      <c r="E42" s="72"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="72"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="72"/>
-      <c r="J42" s="72"/>
-      <c r="K42" s="72"/>
-      <c r="L42" s="72"/>
-      <c r="M42" s="72"/>
-      <c r="N42" s="72"/>
-      <c r="O42" s="72"/>
-      <c r="P42" s="72"/>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43" s="42"/>
-      <c r="B43" s="71" t="s">
+      <c r="C43" s="73"/>
+      <c r="D43" s="73"/>
+    </row>
+    <row r="44" spans="1:16" ht="54" customHeight="1">
+      <c r="A44" s="43"/>
+      <c r="C44" s="74" t="s">
         <v>134</v>
       </c>
-      <c r="C43" s="71"/>
-      <c r="D43" s="71"/>
-    </row>
-    <row r="44" spans="1:16" ht="54" customHeight="1">
-      <c r="A44" s="42"/>
-      <c r="C44" s="72" t="s">
+      <c r="D44" s="74"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="74"/>
+      <c r="H44" s="74"/>
+      <c r="I44" s="74"/>
+      <c r="J44" s="74"/>
+      <c r="K44" s="74"/>
+      <c r="L44" s="74"/>
+      <c r="M44" s="74"/>
+      <c r="N44" s="74"/>
+      <c r="O44" s="74"/>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="43"/>
+      <c r="B45" s="73" t="s">
         <v>135</v>
       </c>
-      <c r="D44" s="72"/>
-      <c r="E44" s="72"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="72"/>
-      <c r="H44" s="72"/>
-      <c r="I44" s="72"/>
-      <c r="J44" s="72"/>
-      <c r="K44" s="72"/>
-      <c r="L44" s="72"/>
-      <c r="M44" s="72"/>
-      <c r="N44" s="72"/>
-      <c r="O44" s="72"/>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="A45" s="42"/>
-      <c r="B45" s="71" t="s">
+      <c r="C45" s="73"/>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="43"/>
+      <c r="C46" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="C45" s="71"/>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46" s="42"/>
-      <c r="C46" s="45" t="s">
+      <c r="D46" s="46"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="46"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="46"/>
+      <c r="K46" s="46"/>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="43"/>
+      <c r="C47" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="45"/>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="A47" s="42"/>
-      <c r="C47" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="45"/>
-      <c r="K47" s="45"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="46"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="46"/>
+      <c r="J47" s="46"/>
+      <c r="K47" s="46"/>
     </row>
     <row r="48" spans="1:16" s="38" customFormat="1"/>
     <row r="49" spans="1:12" ht="46.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B49" s="62" t="s">
         <v>273</v>
       </c>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="58"/>
-      <c r="J49" s="58"/>
-      <c r="K49" s="58"/>
-      <c r="L49" s="58"/>
+      <c r="B49" s="63" t="s">
+        <v>272</v>
+      </c>
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="59"/>
+      <c r="K49" s="59"/>
+      <c r="L49" s="59"/>
     </row>
     <row r="51" spans="1:12" ht="55.5" customHeight="1">
       <c r="A51" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B51" s="78" t="s">
         <v>296</v>
       </c>
-      <c r="B51" s="75" t="s">
-        <v>297</v>
-      </c>
-      <c r="C51" s="75"/>
-      <c r="D51" s="75"/>
-      <c r="E51" s="75"/>
-      <c r="F51" s="75"/>
-      <c r="G51" s="75"/>
-      <c r="H51" s="75"/>
-      <c r="I51" s="75"/>
-      <c r="J51" s="75"/>
-      <c r="K51" s="75"/>
+      <c r="C51" s="78"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="78"/>
+      <c r="F51" s="78"/>
+      <c r="G51" s="78"/>
+      <c r="H51" s="78"/>
+      <c r="I51" s="78"/>
+      <c r="J51" s="78"/>
+      <c r="K51" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="B49:L49"/>
     <mergeCell ref="B51:K51"/>
     <mergeCell ref="B13:L13"/>
     <mergeCell ref="A1:J1"/>
@@ -3944,14 +4365,11 @@
     <mergeCell ref="A12:A21"/>
     <mergeCell ref="C15:L15"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="D21:N21"/>
-    <mergeCell ref="C24:O24"/>
-    <mergeCell ref="C25:O25"/>
     <mergeCell ref="C26:O26"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B49:L49"/>
     <mergeCell ref="D18:N18"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="D19:O19"/>
@@ -3959,6 +4377,15 @@
     <mergeCell ref="A23:A39"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C38:I38"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="D21:N21"/>
+    <mergeCell ref="C24:O24"/>
+    <mergeCell ref="C25:O25"/>
     <mergeCell ref="C47:K47"/>
     <mergeCell ref="A41:A47"/>
     <mergeCell ref="B41:C41"/>
@@ -3967,17 +4394,12 @@
     <mergeCell ref="C44:O44"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="C46:K46"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="C38:I38"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="C30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE1976F-15F1-4C7B-A24A-B1D41A4F072D}">
   <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3988,110 +4410,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="83" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1">
+      <c r="A2" s="82" t="s">
+        <v>282</v>
+      </c>
+      <c r="B2" s="82"/>
+      <c r="C2" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-    </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1">
-      <c r="A2" s="79" t="s">
-        <v>283</v>
-      </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="45" t="s">
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+    </row>
+    <row r="3" spans="1:12" ht="34.5" customHeight="1">
+      <c r="A3" s="82"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="63" t="s">
         <v>276</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-    </row>
-    <row r="3" spans="1:12" ht="34.5" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="62" t="s">
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="82"/>
+      <c r="B4" s="82"/>
+    </row>
+    <row r="5" spans="1:12" ht="38.25" customHeight="1">
+      <c r="A5" s="82"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="79"/>
-      <c r="B4" s="79"/>
-    </row>
-    <row r="5" spans="1:12" ht="38.25" customHeight="1">
-      <c r="A5" s="79"/>
-      <c r="B5" s="79"/>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="63" t="s">
         <v>278</v>
       </c>
-      <c r="D5" s="62" t="s">
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+    </row>
+    <row r="6" spans="1:12" s="22" customFormat="1" ht="83.25" customHeight="1">
+      <c r="A6" s="82"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="43" t="s">
         <v>279</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-    </row>
-    <row r="6" spans="1:12" s="22" customFormat="1" ht="83.25" customHeight="1">
-      <c r="A6" s="79"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="42" t="s">
+      <c r="D6" s="63" t="s">
         <v>280</v>
       </c>
-      <c r="D6" s="62" t="s">
-        <v>281</v>
-      </c>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+      <c r="L6" s="59"/>
     </row>
     <row r="7" spans="1:12" s="22" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="79"/>
-      <c r="B7" s="79"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="62" t="s">
-        <v>288</v>
-      </c>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
+      <c r="A7" s="82"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="63" t="s">
+        <v>287</v>
+      </c>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="39"/>
@@ -4108,70 +4530,70 @@
       <c r="L8" s="39"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="42" t="s">
-        <v>282</v>
-      </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="45" t="s">
-        <v>287</v>
-      </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
+      <c r="A9" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
     </row>
     <row r="10" spans="1:12" ht="41.25" customHeight="1">
-      <c r="A10" s="42"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="62" t="s">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="63" t="s">
+        <v>283</v>
+      </c>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+    </row>
+    <row r="11" spans="1:12" ht="19.5" customHeight="1">
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="59" t="s">
         <v>284</v>
       </c>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
-    </row>
-    <row r="11" spans="1:12" ht="19.5" customHeight="1">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="58" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="46" t="s">
         <v>285</v>
       </c>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="42"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="45" t="s">
-        <v>286</v>
-      </c>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -4193,7 +4615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95CFAAC0-5F12-4C79-B8CF-D835B00C7862}">
   <sheetPr>
     <tabColor theme="1" tint="0.14999847407452621"/>
@@ -4206,119 +4628,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="45" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="44" t="s">
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+    </row>
+    <row r="3" spans="1:9" ht="20.25" customHeight="1">
+      <c r="B3" s="59" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-    </row>
-    <row r="3" spans="1:9" ht="20.25" customHeight="1">
-      <c r="B3" s="58" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="43" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+    </row>
+    <row r="5" spans="1:9" ht="21" customHeight="1">
+      <c r="B5" s="59" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-    </row>
-    <row r="5" spans="1:9" ht="21" customHeight="1">
-      <c r="B5" s="58" t="s">
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="81" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="81"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="C8" s="45" t="s">
-        <v>180</v>
-      </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C9" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="44" t="s">
-        <v>183</v>
-      </c>
-      <c r="B11" s="44"/>
+      <c r="B11" s="45"/>
     </row>
     <row r="12" spans="1:9">
       <c r="B12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="B13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="40.5" customHeight="1">
       <c r="A15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B15" s="67" t="s">
         <v>254</v>
       </c>
-      <c r="B15" s="64" t="s">
-        <v>255</v>
-      </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4337,9 +4759,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3177FA43-C9E8-4CC7-B84D-76C751FF5B02}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="85" customWidth="1"/>
@@ -4349,82 +4771,106 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>142</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" t="s">
         <v>140</v>
-      </c>
-      <c r="B2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" t="s">
         <v>198</v>
-      </c>
-      <c r="B3" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" t="s">
         <v>202</v>
-      </c>
-      <c r="C4" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C5" t="s">
         <v>206</v>
-      </c>
-      <c r="C5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" t="s">
         <v>210</v>
-      </c>
-      <c r="C6" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" t="s">
         <v>208</v>
-      </c>
-      <c r="C7" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B8" t="s">
         <v>290</v>
-      </c>
-      <c r="B8" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
+        <v>303</v>
+      </c>
+      <c r="B9" t="s">
         <v>304</v>
-      </c>
-      <c r="B9" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
+        <v>323</v>
+      </c>
+      <c r="B10" t="s">
         <v>324</v>
       </c>
-      <c r="B10" t="s">
-        <v>325</v>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>371</v>
+      </c>
+      <c r="B11" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>378</v>
+      </c>
+      <c r="C12" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>380</v>
+      </c>
+      <c r="C13" t="s">
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4432,7 +4878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4931D421-F46C-4631-B000-DB2BE8DA1190}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
@@ -4446,81 +4892,81 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="44.25" customHeight="1">
       <c r="A3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="B4" s="43" t="s">
         <v>146</v>
       </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="B4" s="42" t="s">
+      <c r="C4" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="B5" s="43"/>
+      <c r="C5" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="B5" s="42"/>
-      <c r="C5" s="45" t="s">
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="B6" s="43"/>
+      <c r="C6" s="46" t="s">
         <v>149</v>
       </c>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="B6" s="42"/>
-      <c r="C6" s="45" t="s">
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="B7" s="43"/>
+      <c r="C7" s="46" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="B7" s="42"/>
-      <c r="C7" s="45" t="s">
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="B8" s="43"/>
+      <c r="C8" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="B8" s="42"/>
-      <c r="C8" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4536,7 +4982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB8042A-BB9A-4906-86BE-4DCA75FD95FC}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -4551,115 +4997,115 @@
   <sheetData>
     <row r="1" spans="1:15" ht="36" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="82" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
+      <c r="C1" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="11"/>
-      <c r="C3" s="65" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
+      <c r="C3" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4688,61 +5134,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="51" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
     </row>
     <row r="6" spans="1:13">
       <c r="B6" s="6"/>
@@ -4754,179 +5200,179 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
+        <v>19</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="B10" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="B10" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
-      <c r="M12" s="45"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
+      <c r="A14" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
+        <v>29</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
     </row>
     <row r="17" spans="1:9" ht="39.75" customHeight="1">
       <c r="A17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="48" t="s">
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="43" t="s">
+      <c r="B19" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="44" t="s">
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="44"/>
+      <c r="B20" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44" t="s">
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="43" t="s">
+      <c r="B22" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="44" t="s">
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="44"/>
+      <c r="B23" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="43"/>
-      <c r="B23" s="44" t="s">
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
     </row>
     <row r="27" spans="1:9" ht="30">
       <c r="A27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
     </row>
     <row r="29" spans="1:9">
       <c r="B29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -4960,7 +5406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FB3EBF8-D959-461C-841A-4596F001B589}">
-  <dimension ref="A2:B53"/>
+  <dimension ref="A2:B59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -4969,156 +5415,171 @@
   <sheetData>
     <row r="2" spans="1:2" ht="75">
       <c r="B2" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30">
       <c r="A4" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30">
       <c r="B6" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="65.25" customHeight="1">
       <c r="A8" s="3"/>
       <c r="B8" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="45">
       <c r="A10" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45">
       <c r="A12" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="51.75">
       <c r="A16" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="45">
       <c r="B18" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="30">
       <c r="B20" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="45">
       <c r="B22" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="45">
       <c r="B24" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="90">
       <c r="B26" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="45">
       <c r="B27" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="45">
       <c r="B29" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="45">
       <c r="B31" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="30">
       <c r="B33" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="75">
       <c r="B35" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="30">
       <c r="B37" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="B39" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="B41" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="30">
       <c r="B43" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="B45" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B47" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30">
       <c r="A49" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="90">
       <c r="B51" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="45">
       <c r="B53" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="30">
+      <c r="B55" s="8" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="B57" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="30">
+      <c r="B59" s="8" t="s">
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -5142,78 +5603,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.5">
-      <c r="A1" s="55" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="A1" s="56" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="52" t="s">
-        <v>145</v>
-      </c>
-      <c r="B2" s="53"/>
+      <c r="A2" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="54"/>
       <c r="C2" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D2" s="26"/>
       <c r="E2" s="26"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
       <c r="C3" s="27" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D3" s="26"/>
       <c r="E3" s="26"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="53"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="26" t="s">
-        <v>232</v>
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="42" t="s">
+        <v>231</v>
       </c>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="53"/>
-      <c r="B5" s="53"/>
+      <c r="A5" s="54"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="26"/>
     </row>
     <row r="6" spans="1:5" ht="30">
-      <c r="A6" s="53"/>
-      <c r="B6" s="53"/>
+      <c r="A6" s="54"/>
+      <c r="B6" s="54"/>
       <c r="C6" s="27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="53"/>
-      <c r="B7" s="53"/>
+      <c r="A7" s="54"/>
+      <c r="B7" s="54"/>
       <c r="C7" s="26"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="53"/>
-      <c r="B8" s="53"/>
+      <c r="A8" s="54"/>
+      <c r="B8" s="54"/>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
       <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5" ht="30">
-      <c r="A9" s="53"/>
-      <c r="B9" s="53"/>
+      <c r="A9" s="54"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="27" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="26"/>
@@ -5226,30 +5687,30 @@
       <c r="E10" s="31"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="52" t="s">
-        <v>247</v>
-      </c>
-      <c r="B11" s="54"/>
+      <c r="A11" s="53" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" s="55"/>
       <c r="C11" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="54"/>
-      <c r="B12" s="54"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="54"/>
-      <c r="B13" s="54"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="55"/>
       <c r="C13" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="26"/>
@@ -5262,69 +5723,69 @@
       <c r="E14" s="31"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" s="55"/>
+      <c r="C15" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="32" t="s">
+      <c r="D15" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="D15" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="32" t="s">
+    </row>
+    <row r="16" spans="1:5" ht="45">
+      <c r="A16" s="55"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="26" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="45">
-      <c r="A16" s="54"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="26" t="s">
+      <c r="D16" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>241</v>
-      </c>
       <c r="E16" s="27" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="54"/>
-      <c r="B17" s="54"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="55"/>
       <c r="C17" s="26"/>
       <c r="D17" s="26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E17" s="26"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="54"/>
-      <c r="B18" s="54"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="55"/>
       <c r="C18" s="26"/>
       <c r="D18" s="26" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="54"/>
-      <c r="B19" s="54"/>
+      <c r="A19" s="55"/>
+      <c r="B19" s="55"/>
       <c r="C19" s="26"/>
       <c r="D19" s="26"/>
       <c r="E19" s="26"/>
     </row>
     <row r="20" spans="1:5" ht="30">
-      <c r="A20" s="54"/>
-      <c r="B20" s="54"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="55"/>
       <c r="C20" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="E20" s="27" t="s">
         <v>244</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -5351,17 +5812,17 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="2:2" ht="45">
       <c r="B3" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="45">
       <c r="B5" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -5371,7 +5832,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8311B8EB-D940-4C05-A7EB-036127FEA15A}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="43.140625" customWidth="1"/>
@@ -5381,57 +5842,79 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1" t="s">
         <v>220</v>
-      </c>
-      <c r="B1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45">
       <c r="A2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" t="s">
         <v>223</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="20" t="s">
         <v>224</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" t="s">
         <v>298</v>
-      </c>
-      <c r="B3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30">
       <c r="A4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>300</v>
-      </c>
-      <c r="B4" t="s">
-        <v>222</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30">
       <c r="A5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>303</v>
+    </row>
+    <row r="6" spans="1:3" ht="30">
+      <c r="A6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B6" t="s">
+        <v>364</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30">
+      <c r="A8" t="s">
+        <v>369</v>
+      </c>
+      <c r="B8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -5449,122 +5932,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30.75" customHeight="1">
-      <c r="A1" s="57" t="s">
-        <v>153</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="A1" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
     </row>
     <row r="3" spans="1:13">
       <c r="B3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="58" t="s">
-        <v>157</v>
-      </c>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
     </row>
     <row r="4" spans="1:13">
       <c r="B4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="46" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" t="s">
         <v>160</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
     </row>
     <row r="7" spans="1:13">
       <c r="B7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>164</v>
-      </c>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
     </row>
     <row r="8" spans="1:13">
       <c r="B8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="46" t="s">
         <v>165</v>
       </c>
-      <c r="C8" s="45" t="s">
-        <v>166</v>
-      </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5592,82 +6075,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="40" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A1" s="60" t="s">
-        <v>323</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
+      <c r="A1" s="61" t="s">
+        <v>322</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
       <c r="M1" s="20"/>
       <c r="N1" s="20"/>
       <c r="O1" s="20"/>
       <c r="P1" s="20"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="B2" s="58" t="s">
+      <c r="A2" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="43"/>
+      <c r="B3" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="42"/>
-      <c r="B3" s="45" t="s">
-        <v>307</v>
-      </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="42"/>
-      <c r="B4" s="58" t="s">
+      <c r="A4" s="43"/>
+      <c r="B4" s="59" t="s">
+        <v>309</v>
+      </c>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="43"/>
+      <c r="B5" s="59" t="s">
         <v>310</v>
       </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" s="42"/>
-      <c r="B5" s="58" t="s">
-        <v>311</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="41"/>
@@ -5684,20 +6167,20 @@
     </row>
     <row r="7" spans="1:16" ht="43.5" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B7" s="63" t="s">
         <v>308</v>
       </c>
-      <c r="B7" s="62" t="s">
-        <v>309</v>
-      </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="41"/>
@@ -5713,66 +6196,66 @@
       <c r="K8" s="41"/>
     </row>
     <row r="9" spans="1:16" ht="38.25" customHeight="1">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="60" t="s">
+        <v>311</v>
+      </c>
+      <c r="B9" s="63" t="s">
         <v>312</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="59"/>
+    </row>
+    <row r="10" spans="1:16" ht="20.25" customHeight="1">
+      <c r="A10" s="60"/>
+      <c r="B10" s="59" t="s">
         <v>313</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-    </row>
-    <row r="10" spans="1:16" ht="20.25" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="58" t="s">
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+    </row>
+    <row r="11" spans="1:16" ht="41.25" customHeight="1">
+      <c r="A11" s="60"/>
+      <c r="B11" s="63" t="s">
         <v>314</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-    </row>
-    <row r="11" spans="1:16" ht="41.25" customHeight="1">
-      <c r="A11" s="59"/>
-      <c r="B11" s="62" t="s">
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+    </row>
+    <row r="12" spans="1:16" ht="21" customHeight="1">
+      <c r="A12" s="60"/>
+      <c r="B12" s="59" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="62"/>
-    </row>
-    <row r="12" spans="1:16" ht="21" customHeight="1">
-      <c r="A12" s="59"/>
-      <c r="B12" s="58" t="s">
-        <v>316</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="59"/>
+      <c r="K12" s="59"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="41"/>
@@ -5789,21 +6272,21 @@
     </row>
     <row r="14" spans="1:16" ht="43.5" customHeight="1">
       <c r="A14" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B14" s="63" t="s">
         <v>317</v>
       </c>
-      <c r="B14" s="62" t="s">
-        <v>318</v>
-      </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="62"/>
-      <c r="L14" s="62"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="63"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="41"/>
@@ -5819,64 +6302,64 @@
       <c r="K15" s="41"/>
     </row>
     <row r="16" spans="1:16" ht="30" customHeight="1">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
+        <v>318</v>
+      </c>
+      <c r="B16" s="59" t="s">
         <v>319</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59"/>
+      <c r="K16" s="59"/>
+    </row>
+    <row r="17" spans="1:20" ht="30" customHeight="1">
+      <c r="A17" s="60"/>
+      <c r="B17" s="63" t="s">
         <v>320</v>
       </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-    </row>
-    <row r="17" spans="1:20" ht="30" customHeight="1">
-      <c r="A17" s="59"/>
-      <c r="B17" s="62" t="s">
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" s="60"/>
+      <c r="B18" s="44" t="s">
         <v>321</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="59"/>
-      <c r="B18" s="43" t="s">
-        <v>322</v>
-      </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
     </row>
     <row r="21" spans="1:20">
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="62"/>
-      <c r="P21" s="62"/>
-      <c r="Q21" s="62"/>
-      <c r="R21" s="62"/>
-      <c r="S21" s="62"/>
-      <c r="T21" s="62"/>
+      <c r="J21" s="63"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="63"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="63"/>
+      <c r="P21" s="63"/>
+      <c r="Q21" s="63"/>
+      <c r="R21" s="63"/>
+      <c r="S21" s="63"/>
+      <c r="T21" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -5904,126 +6387,291 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{055368DB-E282-4263-B8BF-74FF1A138266}">
-  <sheetPr>
-    <tabColor theme="5" tint="0.39997558519241921"/>
-  </sheetPr>
-  <dimension ref="A2:F8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E15CDB-E1B6-4AA1-A152-149FEEAF29BE}">
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6">
-      <c r="A2" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="D2" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="F2" s="37" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="45">
-      <c r="A3" s="42"/>
-      <c r="B3" s="37" t="s">
-        <v>262</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="30">
-      <c r="A4" s="42"/>
-      <c r="B4" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>269</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>270</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="30">
-      <c r="A5" s="42"/>
-      <c r="B5" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>269</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>270</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="42"/>
-      <c r="B6" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>269</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>269</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="41.25" customHeight="1">
-      <c r="B8" s="62" t="s">
-        <v>289</v>
-      </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
+    <row r="1" spans="1:8" ht="28.5" customHeight="1">
+      <c r="A1" s="40" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A2" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>328</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+    </row>
+    <row r="3" spans="1:8" ht="18.75" customHeight="1">
+      <c r="A3" s="43"/>
+      <c r="B3" s="59" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+    </row>
+    <row r="4" spans="1:8" ht="36" customHeight="1">
+      <c r="A4" s="43"/>
+      <c r="B4" s="63" t="s">
+        <v>330</v>
+      </c>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="43" t="s">
+        <v>334</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>331</v>
+      </c>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="43"/>
+      <c r="B7" s="59" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="43"/>
+      <c r="B8" s="59" t="s">
+        <v>333</v>
+      </c>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+    </row>
+    <row r="10" spans="1:8" ht="18.75" customHeight="1">
+      <c r="A10" s="43" t="s">
+        <v>335</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60" t="s">
+        <v>336</v>
+      </c>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+    </row>
+    <row r="11" spans="1:8" ht="26.25" customHeight="1">
+      <c r="A11" s="43"/>
+      <c r="B11" s="63" t="s">
+        <v>337</v>
+      </c>
+      <c r="C11" s="63"/>
+      <c r="D11" s="64" t="s">
+        <v>339</v>
+      </c>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+    </row>
+    <row r="12" spans="1:8" ht="40.5" customHeight="1">
+      <c r="A12" s="43"/>
+      <c r="B12" s="63" t="s">
+        <v>338</v>
+      </c>
+      <c r="C12" s="63"/>
+      <c r="D12" s="65" t="s">
+        <v>340</v>
+      </c>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+    </row>
+    <row r="14" spans="1:8" ht="30" customHeight="1">
+      <c r="A14" s="60" t="s">
+        <v>341</v>
+      </c>
+      <c r="B14" s="59" t="s">
+        <v>345</v>
+      </c>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+    </row>
+    <row r="15" spans="1:8" ht="19.5" customHeight="1">
+      <c r="A15" s="60"/>
+      <c r="B15" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="59"/>
+    </row>
+    <row r="16" spans="1:8" ht="19.5" customHeight="1">
+      <c r="A16" s="60"/>
+      <c r="B16" s="59" t="s">
+        <v>343</v>
+      </c>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+    </row>
+    <row r="17" spans="1:8" ht="20.25" customHeight="1">
+      <c r="A17" s="60"/>
+      <c r="B17" s="59" t="s">
+        <v>344</v>
+      </c>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+    </row>
+    <row r="19" spans="1:8" ht="30" customHeight="1">
+      <c r="A19" s="60" t="s">
+        <v>346</v>
+      </c>
+      <c r="B19" s="59" t="s">
+        <v>347</v>
+      </c>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="60"/>
+      <c r="B20" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="60"/>
+      <c r="B21" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="60"/>
+      <c r="B22" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="60"/>
+      <c r="B23" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="43" t="s">
+        <v>352</v>
+      </c>
+      <c r="B25" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="43"/>
+      <c r="B26" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="43"/>
+      <c r="B27" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="43"/>
+      <c r="B28" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="43"/>
+      <c r="B29" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="43"/>
+      <c r="B30" t="s">
+        <v>358</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B8:F8"/>
+  <mergeCells count="23">
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="A25:A30"/>
+    <mergeCell ref="B16:H16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
